--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2532-5</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2535-5</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2536-5</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-5</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2540-5</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2542-5</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2544-6</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-5</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP9750-0</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-6</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>LDP003</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP007</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP009</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LE2851</t>
         </is>
       </c>
     </row>
@@ -2777,3846 +2777,3891 @@
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2852</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7007</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4009</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7008</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4011</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7012</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4012</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7014</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4013</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7015</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>Q4014</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>S7018</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>Q4015</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>S7020</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>Q4016</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>S7022</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>Q4017</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>Q4019</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT002</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QBX003</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT006</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QBX004</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT007</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QBX005</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT009</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QBX006</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT011</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QE001</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SCT013</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QE002</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SCT014</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QE003</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SCT015</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QE004</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SO2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QE006</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SSR101</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL001</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>SSR102</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL002</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>SSR103</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL004</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>SSR104</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL007</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>T363</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QL008</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>T386</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QL010</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TDX101</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QL011</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2801</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>QL014</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2802</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>QL018</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2803</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>QR1744</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2804</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>QR1771</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2805</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>QR5404</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2806</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>R711</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2807</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>R766</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2808</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RB2353</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2809</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RCTST4</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2810</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL301</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TE2812</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>RL302</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TE2813</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>RL304</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TE2814</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>RL307</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TJ096</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>RL309</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TJ107</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>RL310</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT03</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S312</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT04</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S317</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT05</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3301</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT07</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3302</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT08</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8812</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8803</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8804</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8805</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8806</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -484,32 +484,32 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -526,32 +526,32 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -568,32 +568,32 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -610,32 +610,32 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -652,32 +652,32 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -694,32 +694,32 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -736,32 +736,32 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -778,32 +778,32 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -815,37 +815,37 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3VL103</t>
+          <t>3VL101</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>3VL104</t>
+          <t>3VL103</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3VL105</t>
+          <t>3VL104</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>3VL106</t>
+          <t>3VL105</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -983,37 +983,37 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>3VL107</t>
+          <t>3VL106</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>3VL109</t>
+          <t>3VL107</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1067,37 +1067,37 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>3VL110</t>
+          <t>3VL109</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>3VL112</t>
+          <t>3VL110</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1151,37 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>3VL113</t>
+          <t>3VL112</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>3VL114</t>
+          <t>3VL113</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1235,37 +1235,37 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>3VL115</t>
+          <t>3VL114</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>3VL116</t>
+          <t>3VL115</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1319,37 +1319,37 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3VL117</t>
+          <t>3VL116</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1361,37 +1361,37 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3VL118</t>
+          <t>3VL117</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1403,37 +1403,37 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3VL119</t>
+          <t>3VL118</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -1445,37 +1445,37 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>3VL120</t>
+          <t>3VL119</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -1487,37 +1487,37 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>3VL121</t>
+          <t>3VL120</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>3VL123</t>
+          <t>3VL121</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1571,37 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>3VL124</t>
+          <t>3VL123</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -1613,37 +1613,37 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3VL125</t>
+          <t>3VL124</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3VL126</t>
+          <t>3VL125</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>3VL127</t>
+          <t>3VL126</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>3VL128</t>
+          <t>3VL127</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -1781,37 +1781,37 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>3VL131</t>
+          <t>3VL128</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -1823,37 +1823,37 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>3VL133</t>
+          <t>3VL131</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>3VL134</t>
+          <t>3VL133</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -1907,37 +1907,37 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>3VL135</t>
+          <t>3VL134</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>3VL136</t>
+          <t>3VL135</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -1991,37 +1991,37 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>3VL137</t>
+          <t>3VL136</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -2033,37 +2033,37 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>3VL139</t>
+          <t>3VL137</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -2075,37 +2075,37 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>3VR78</t>
+          <t>3VL139</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2117,37 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>3VS93</t>
+          <t>3VR78</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
@@ -2159,37 +2159,37 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>3VS94</t>
+          <t>3VS93</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
@@ -2201,37 +2201,37 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3VS95</t>
+          <t>3VS94</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2474-5</t>
         </is>
       </c>
     </row>
@@ -2243,37 +2243,37 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>3VS96</t>
+          <t>3VS95</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
     </row>
@@ -2285,37 +2285,37 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>3VS97</t>
+          <t>3VS96</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G522</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2532-5</t>
         </is>
       </c>
     </row>
@@ -2327,37 +2327,37 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>3VS98</t>
+          <t>3VS97</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G524</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2535-0</t>
         </is>
       </c>
     </row>
@@ -2369,37 +2369,37 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3VS98</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G525</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2535-5</t>
         </is>
       </c>
     </row>
@@ -2411,37 +2411,37 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>G526</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2536-5</t>
         </is>
       </c>
     </row>
@@ -2453,37 +2453,37 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>G533</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
     </row>
@@ -2495,37 +2495,37 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>G534</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2537-5</t>
         </is>
       </c>
     </row>
@@ -2537,37 +2537,37 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>G543</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2540-5</t>
         </is>
       </c>
     </row>
@@ -2579,37 +2579,37 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL104</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP2541-0</t>
         </is>
       </c>
     </row>
@@ -2621,37 +2621,37 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GL105</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP2542-1</t>
         </is>
       </c>
     </row>
@@ -2663,37 +2663,37 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GL108</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>JP2542-5</t>
         </is>
       </c>
     </row>
@@ -2705,37 +2705,37 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GL109</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>JP2544-6</t>
         </is>
       </c>
     </row>
@@ -2747,3921 +2747,4011 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GL111</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>JP2546-5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7007</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>Q4009</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>S7008</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>Q4011</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>S7012</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>Q4012</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>S7014</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>Q4013</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>S7015</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>Q4014</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>S7018</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>Q4015</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>S7020</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>Q4016</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>S7022</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>Q4017</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT001</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>Q4019</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT002</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QBX003</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SCT006</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QBX004</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SCT007</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QBX005</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SCT009</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QBX006</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SCT011</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QE001</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SCT013</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QE002</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>SCT014</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QE003</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>SCT015</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QE004</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>SO2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QE006</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>SSR101</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QL001</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>SSR102</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QL002</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>SSR103</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QL004</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>SSR104</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>QL007</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>T363</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>QL008</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>T386</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>QL010</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TDX101</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>QL011</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2801</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>QL014</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2802</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>QL018</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2803</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>QR1744</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2804</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>QR1771</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2805</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>QR5404</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2806</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>R711</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TE2807</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8778</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8780</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8793</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8795</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8797</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8799</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8800</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8801</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8802</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8803</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8804</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8805</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8806</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8812</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -447,27 +447,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -489,27 +489,27 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -531,27 +531,27 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -573,27 +573,27 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -615,27 +615,27 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -657,27 +657,27 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -699,27 +699,27 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -741,27 +741,27 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -825,27 +825,27 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -867,27 +867,27 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -909,27 +909,27 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -951,27 +951,27 @@
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -993,27 +993,27 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1035,27 +1035,27 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1119,27 +1119,27 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1161,27 +1161,27 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1203,27 +1203,27 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1245,27 +1245,27 @@
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1287,27 +1287,27 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1329,27 +1329,27 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1371,27 +1371,27 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1413,27 +1413,27 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1455,27 +1455,27 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1497,27 +1497,27 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1539,27 +1539,27 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -1581,27 +1581,27 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -1623,27 +1623,27 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -1665,27 +1665,27 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -1749,27 +1749,27 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -1791,27 +1791,27 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -1833,27 +1833,27 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -1875,27 +1875,27 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -1917,27 +1917,27 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -1959,27 +1959,27 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2001,27 +2001,27 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2043,27 +2043,27 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2080,32 +2080,32 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -2122,32 +2122,32 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -2164,32 +2164,32 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
@@ -2248,32 +2248,32 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
@@ -2290,32 +2290,32 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
     </row>
@@ -2374,32 +2374,32 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
     </row>
@@ -2416,32 +2416,32 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G522</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2532-5</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G524</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2535-0</t>
         </is>
       </c>
     </row>
@@ -2500,32 +2500,32 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G525</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2535-5</t>
         </is>
       </c>
     </row>
@@ -2542,32 +2542,32 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G526</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2536-5</t>
         </is>
       </c>
     </row>
@@ -2584,32 +2584,32 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G533</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2537-1</t>
         </is>
       </c>
     </row>
@@ -2626,32 +2626,32 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>G534</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2537-5</t>
         </is>
       </c>
     </row>
@@ -2668,32 +2668,32 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>G543</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2540-5</t>
         </is>
       </c>
     </row>
@@ -2710,32 +2710,32 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL104</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2541-0</t>
         </is>
       </c>
     </row>
@@ -2752,4006 +2752,4136 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL105</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7007</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4009</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7008</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4011</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7012</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4012</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7014</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4013</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7015</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4014</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7018</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4015</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7020</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4016</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7022</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>Q4017</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT001</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>Q4019</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT002</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX003</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT006</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX004</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT007</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QBX005</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT009</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QBX006</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT011</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE001</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT013</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE002</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT014</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE003</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT015</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QE004</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SO2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QE006</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR101</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL001</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR102</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL002</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SSR103</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL004</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SSR104</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL007</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>T363</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL008</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>T386</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL010</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TDX101</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL011</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2801</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8768</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8770</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8772</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8774</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8776</t>
+        </is>
+      </c>
+      <c r="F141" s="1" t="inlineStr">
+        <is>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8778</t>
+        </is>
+      </c>
+      <c r="F142" s="1" t="inlineStr">
+        <is>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8780</t>
+        </is>
+      </c>
+      <c r="F143" s="1" t="inlineStr">
+        <is>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8782</t>
+        </is>
+      </c>
+      <c r="F144" s="1" t="inlineStr">
+        <is>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8784</t>
+        </is>
+      </c>
+      <c r="F145" s="1" t="inlineStr">
+        <is>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8786</t>
+        </is>
+      </c>
+      <c r="F146" s="1" t="inlineStr">
+        <is>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8793</t>
+        </is>
+      </c>
+      <c r="F147" s="1" t="inlineStr">
+        <is>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8795</t>
+        </is>
+      </c>
+      <c r="F148" s="1" t="inlineStr">
+        <is>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8797</t>
+        </is>
+      </c>
+      <c r="F149" s="1" t="inlineStr">
+        <is>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8799</t>
+        </is>
+      </c>
+      <c r="F150" s="1" t="inlineStr">
+        <is>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8800</t>
+        </is>
+      </c>
+      <c r="F151" s="1" t="inlineStr">
+        <is>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8801</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="inlineStr">
+        <is>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8802</t>
+        </is>
+      </c>
+      <c r="F153" s="1" t="inlineStr">
+        <is>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8803</t>
+        </is>
+      </c>
+      <c r="F154" s="1" t="inlineStr">
+        <is>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8804</t>
+        </is>
+      </c>
+      <c r="F155" s="1" t="inlineStr">
+        <is>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8805</t>
+        </is>
+      </c>
+      <c r="F156" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8806</t>
+        </is>
+      </c>
+      <c r="F157" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="F160" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="F161" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>VLINE-8812</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -437,37 +437,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3VL85</t>
+          <t>3VL83</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>3VL86</t>
+          <t>3VL85</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -521,37 +521,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>3VL87</t>
+          <t>3VL86</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>3VL88</t>
+          <t>3VL87</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -605,37 +605,37 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3VL89</t>
+          <t>3VL88</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -647,37 +647,37 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>3VL90</t>
+          <t>3VL89</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -689,37 +689,37 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>3VL91</t>
+          <t>3VL90</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -731,37 +731,37 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>3VL99</t>
+          <t>3VL91</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>3VL100</t>
+          <t>3VL99</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -815,37 +815,37 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3VL101</t>
+          <t>3VL100</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>3VL103</t>
+          <t>3VL101</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3VL104</t>
+          <t>3VL103</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>3VL105</t>
+          <t>3VL104</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -983,37 +983,37 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>3VL106</t>
+          <t>3VL105</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>3VL107</t>
+          <t>3VL106</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1067,37 +1067,37 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>3VL109</t>
+          <t>3VL107</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>3VL110</t>
+          <t>3VL109</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1151,37 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>3VL112</t>
+          <t>3VL110</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>3VL113</t>
+          <t>3VL112</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1235,37 +1235,37 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>3VL114</t>
+          <t>3VL113</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>3VL115</t>
+          <t>3VL114</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1319,37 +1319,37 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3VL116</t>
+          <t>3VL115</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1361,37 +1361,37 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3VL117</t>
+          <t>3VL116</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1403,37 +1403,37 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3VL118</t>
+          <t>3VL117</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1445,37 +1445,37 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>3VL119</t>
+          <t>3VL118</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1487,37 +1487,37 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>3VL120</t>
+          <t>3VL119</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>3VL121</t>
+          <t>3VL120</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1571,37 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>3VL123</t>
+          <t>3VL121</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1613,37 +1613,37 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3VL124</t>
+          <t>3VL123</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3VL125</t>
+          <t>3VL124</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>3VL126</t>
+          <t>3VL125</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>3VL127</t>
+          <t>3VL126</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -1781,37 +1781,37 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>3VL128</t>
+          <t>3VL127</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -1823,37 +1823,37 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>3VL131</t>
+          <t>3VL128</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>3VL133</t>
+          <t>3VL131</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -1907,37 +1907,37 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>3VL134</t>
+          <t>3VL133</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>3VL135</t>
+          <t>3VL134</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -1991,37 +1991,37 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>3VL136</t>
+          <t>3VL135</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -2033,37 +2033,37 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>3VL137</t>
+          <t>3VL136</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -2075,37 +2075,37 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>3VL139</t>
+          <t>3VL137</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2117,37 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>3VR78</t>
+          <t>3VL139</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2159,37 +2159,37 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>3VS93</t>
+          <t>3VR78</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
@@ -2201,37 +2201,37 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3VS94</t>
+          <t>3VS93</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2243,37 +2243,37 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>3VS95</t>
+          <t>3VS94</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -2285,4603 +2285,4733 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>3VS96</t>
+          <t>3VS95</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>3VL63</t>
+          <t>3VL62</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>3VS97</t>
+          <t>3VS96</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>3VL64</t>
+          <t>3VL63</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>3VS98</t>
+          <t>3VS97</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>3VL65</t>
+          <t>3VL64</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3VS98</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>3VL68</t>
+          <t>3VL65</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2338-0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>3VL70</t>
+          <t>3VL68</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>3VL71</t>
+          <t>3VL70</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G522</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2341-0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>3VL72</t>
+          <t>3VL71</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G524</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2474-5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>3VL75</t>
+          <t>3VL72</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G525</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>3VL80</t>
+          <t>3VL75</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G526</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2532-5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>3VL81</t>
+          <t>3VL80</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G533</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2535-0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>3VL83</t>
+          <t>3VL81</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>G534</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2535-5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7007</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4009</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7008</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4011</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7012</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4012</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7014</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4013</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7015</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>Q4014</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>S7017</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>Q4015</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>S7018</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>Q4016</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>S7020</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>Q4017</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>S7022</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>Q4019</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT001</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QBX003</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT002</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QBX004</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT006</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QBX005</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT007</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QBX006</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT009</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QE001</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SCT011</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QE002</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SCT013</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QE003</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SCT014</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8790</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8793</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8795</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8797</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8799</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8800</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8801</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8802</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8803</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8804</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8805</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8806</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8776</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="inlineStr">
+        <is>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8778</t>
+        </is>
+      </c>
+      <c r="F164" s="1" t="inlineStr">
+        <is>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8779</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="inlineStr">
+        <is>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8780</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="inlineStr">
+        <is>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8782</t>
+        </is>
+      </c>
+      <c r="F167" s="1" t="inlineStr">
+        <is>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8784</t>
+        </is>
+      </c>
+      <c r="F168" s="1" t="inlineStr">
+        <is>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8786</t>
+        </is>
+      </c>
+      <c r="F169" s="1" t="inlineStr">
+        <is>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8788</t>
+        </is>
+      </c>
+      <c r="F170" s="1" t="inlineStr">
+        <is>
+          <t>XP2019</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -437,37 +437,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3VL83</t>
+          <t>3VL81</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>3VL85</t>
+          <t>3VL83</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -521,37 +521,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>3VL86</t>
+          <t>3VL85</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>3VL87</t>
+          <t>3VL86</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -605,37 +605,37 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3VL88</t>
+          <t>3VL87</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -647,37 +647,37 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>3VL89</t>
+          <t>3VL88</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -689,37 +689,37 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>3VL90</t>
+          <t>3VL89</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -731,37 +731,37 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>3VL91</t>
+          <t>3VL90</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>3VL99</t>
+          <t>3VL91</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -815,37 +815,37 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3VL100</t>
+          <t>3VL99</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -857,442 +857,442 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>3VL101</t>
+          <t>3VL100</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>3VL17</t>
+          <t>3VL16</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3VL103</t>
+          <t>3VL101</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>3VL18</t>
+          <t>3VL17</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>3VL104</t>
+          <t>3VL103</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>3VL19</t>
+          <t>3VL18</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>3VL105</t>
+          <t>3VL104</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>3VL20</t>
+          <t>3VL19</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>3VL106</t>
+          <t>3VL105</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>3VL21</t>
+          <t>3VL20</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>3VL107</t>
+          <t>3VL106</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>3VL23</t>
+          <t>3VL21</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>3VL109</t>
+          <t>3VL107</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>3VL24</t>
+          <t>3VL23</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>3VL110</t>
+          <t>3VL109</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>3VL25</t>
+          <t>3VL24</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>3VL112</t>
+          <t>3VL110</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>3VL26</t>
+          <t>3VL25</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>3VL113</t>
+          <t>3VL112</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>3VL28</t>
+          <t>3VL26</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>3VL114</t>
+          <t>3VL113</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
@@ -1302,5716 +1302,5776 @@
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>3VL30</t>
+          <t>3VL28</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3VL115</t>
+          <t>3VL114</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>3VL31</t>
+          <t>3VL30</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3VL116</t>
+          <t>3VL115</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>3VL32</t>
+          <t>3VL31</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3VL117</t>
+          <t>3VL116</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>3VL33</t>
+          <t>3VL32</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>3VL118</t>
+          <t>3VL117</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>3VL34</t>
+          <t>3VL33</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>3VL119</t>
+          <t>3VL118</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>3VL35</t>
+          <t>3VL34</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>3VL120</t>
+          <t>3VL119</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>3VL36</t>
+          <t>3VL35</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>3VL121</t>
+          <t>3VL120</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>3VL37</t>
+          <t>3VL36</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3VL123</t>
+          <t>3VL121</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>3VL39</t>
+          <t>3VL37</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3VL124</t>
+          <t>3VL123</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>3VL40</t>
+          <t>3VL39</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>3VL125</t>
+          <t>3VL124</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>3VL41</t>
+          <t>3VL40</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>3VL126</t>
+          <t>3VL125</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>3VL43</t>
+          <t>3VL41</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>3VL127</t>
+          <t>3VL126</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>3VL44</t>
+          <t>3VL43</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>3VL128</t>
+          <t>3VL127</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>3VL45</t>
+          <t>3VL44</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>3VL131</t>
+          <t>3VL128</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>3VL46</t>
+          <t>3VL45</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>3VL133</t>
+          <t>3VL131</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>3VL47</t>
+          <t>3VL46</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>3VL134</t>
+          <t>3VL133</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>3VL48</t>
+          <t>3VL47</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>3VL135</t>
+          <t>3VL134</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>3VL49</t>
+          <t>3VL48</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>3VL136</t>
+          <t>3VL135</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>3VL50</t>
+          <t>3VL49</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>3VL137</t>
+          <t>3VL136</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>3VL52</t>
+          <t>3VL50</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>3VL139</t>
+          <t>3VL137</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>3VL53</t>
+          <t>3VL52</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>3VR78</t>
+          <t>3VL139</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>3VL54</t>
+          <t>3VL53</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3VS93</t>
+          <t>3VR78</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>3VL55</t>
+          <t>3VL54</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>3VS94</t>
+          <t>3VS93</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>3VL59</t>
+          <t>3VL55</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>3VS95</t>
+          <t>3VS94</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>3VL62</t>
+          <t>3VL59</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>3VS96</t>
+          <t>3VS95</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>3VL63</t>
+          <t>3VL62</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>3VS97</t>
+          <t>3VS96</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>3VL64</t>
+          <t>3VL63</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>3VS98</t>
+          <t>3VS97</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>3VL65</t>
+          <t>3VL64</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3VS98</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>3VL68</t>
+          <t>3VL65</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2338-0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>3VL70</t>
+          <t>3VL68</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>3VL71</t>
+          <t>3VL70</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G522</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2341-0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>3VL72</t>
+          <t>3VL71</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G524</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>3VL75</t>
+          <t>3VL72</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G525</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>3VL80</t>
+          <t>3VL75</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G526</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>3VL81</t>
+          <t>3VL80</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G533</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2535-0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7007</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4009</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7008</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4011</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7012</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4012</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7014</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4013</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7015</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4014</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7017</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4015</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7018</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4016</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7020</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4017</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7022</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4019</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>SCT001</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX003</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>SCT002</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QBX004</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT006</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX005</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT007</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8801</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8802</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8803</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
+        <is>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8804</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8805</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8806</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G142" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -437,37 +437,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3VL81</t>
+          <t>3VL80</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G533</t>
         </is>
       </c>
     </row>
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>3VL83</t>
+          <t>3VL81</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -521,37 +521,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>3VL85</t>
+          <t>3VL83</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>3VL86</t>
+          <t>3VL85</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -605,37 +605,37 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3VL87</t>
+          <t>3VL86</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -647,37 +647,37 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>3VL88</t>
+          <t>3VL87</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -689,37 +689,37 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>3VL89</t>
+          <t>3VL88</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -731,37 +731,37 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>3VL90</t>
+          <t>3VL89</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>3VL91</t>
+          <t>3VL90</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -815,37 +815,37 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3VL99</t>
+          <t>3VL91</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>3VL100</t>
+          <t>3VL99</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3VL101</t>
+          <t>3VL100</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>3VL103</t>
+          <t>3VL101</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -983,37 +983,37 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>3VL104</t>
+          <t>3VL103</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>3VL105</t>
+          <t>3VL104</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -1067,37 +1067,37 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>3VL106</t>
+          <t>3VL105</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>3VL107</t>
+          <t>3VL106</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1151,37 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>3VL109</t>
+          <t>3VL107</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>3VL110</t>
+          <t>3VL109</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1235,37 +1235,37 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>3VL112</t>
+          <t>3VL110</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>3VL113</t>
+          <t>3VL112</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1319,22 +1319,22 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3VL114</t>
+          <t>3VL113</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1361,37 +1361,37 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3VL115</t>
+          <t>3VL114</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1403,37 +1403,37 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3VL116</t>
+          <t>3VL115</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1445,37 +1445,37 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>3VL117</t>
+          <t>3VL116</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1487,37 +1487,37 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>3VL118</t>
+          <t>3VL117</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>3VL119</t>
+          <t>3VL118</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1571,37 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>3VL120</t>
+          <t>3VL119</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1613,37 +1613,37 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3VL121</t>
+          <t>3VL120</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3VL123</t>
+          <t>3VL121</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>3VL124</t>
+          <t>3VL123</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>3VL125</t>
+          <t>3VL124</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -1781,37 +1781,37 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>3VL126</t>
+          <t>3VL125</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -1823,37 +1823,37 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>3VL127</t>
+          <t>3VL126</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>3VL128</t>
+          <t>3VL127</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -1907,37 +1907,37 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>3VL131</t>
+          <t>3VL128</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>3VL133</t>
+          <t>3VL131</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -1991,37 +1991,37 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>3VL134</t>
+          <t>3VL133</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -2033,37 +2033,37 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>3VL135</t>
+          <t>3VL134</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -2075,37 +2075,37 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>3VL136</t>
+          <t>3VL135</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2117,37 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>3VL137</t>
+          <t>3VL136</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -2159,37 +2159,37 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>3VL139</t>
+          <t>3VL137</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2201,37 +2201,37 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3VR78</t>
+          <t>3VL139</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2243,37 +2243,37 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>3VS93</t>
+          <t>3VR78</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
@@ -2285,37 +2285,37 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>3VS94</t>
+          <t>3VS93</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2327,37 +2327,37 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>3VS95</t>
+          <t>3VS94</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -2369,37 +2369,37 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>3VS96</t>
+          <t>3VS95</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -2411,37 +2411,37 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>3VS97</t>
+          <t>3VS96</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -2453,37 +2453,37 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>3VS98</t>
+          <t>3VS97</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
@@ -2495,37 +2495,37 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3VS98</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
@@ -2537,37 +2537,37 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2338-0</t>
         </is>
       </c>
     </row>
@@ -2579,37 +2579,37 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
@@ -2621,37 +2621,37 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G522</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2341-0</t>
         </is>
       </c>
     </row>
@@ -2663,4415 +2663,4445 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G524</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>3VL75</t>
+          <t>3VL74</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G525</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>3VL80</t>
+          <t>3VL75</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G526</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4009</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7007</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4011</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7008</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4012</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7012</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4013</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7014</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4014</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7015</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4015</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7017</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4016</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7018</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="G147" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="G149" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G150" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -452,22 +452,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G524</t>
         </is>
       </c>
     </row>
@@ -494,22 +494,22 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G525</t>
         </is>
       </c>
     </row>
@@ -536,22 +536,22 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G526</t>
         </is>
       </c>
     </row>
@@ -578,22 +578,22 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G533</t>
         </is>
       </c>
     </row>
@@ -620,22 +620,22 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>G539</t>
         </is>
       </c>
     </row>
@@ -704,22 +704,22 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -830,22 +830,22 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -872,22 +872,22 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -998,22 +998,22 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -1040,22 +1040,22 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -1124,22 +1124,22 @@
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -1208,22 +1208,22 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -1250,22 +1250,22 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1292,22 +1292,22 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1334,22 +1334,22 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1376,22 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1544,22 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1586,22 +1586,22 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1628,22 +1628,22 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1670,22 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1712,22 +1712,22 @@
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1754,22 +1754,22 @@
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1838,22 +1838,22 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1880,22 +1880,22 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1922,22 +1922,22 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -1964,22 +1964,22 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -2006,22 +2006,22 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -2048,22 +2048,22 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6047</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -2132,22 +2132,22 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -2174,22 +2174,22 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -2216,22 +2216,22 @@
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -2258,22 +2258,22 @@
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -2300,22 +2300,22 @@
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -2342,22 +2342,22 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2379,27 +2379,27 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2421,27 +2421,27 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
@@ -2463,27 +2463,27 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2505,27 +2505,27 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -2547,27 +2547,27 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -2589,27 +2589,27 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -2631,27 +2631,27 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
@@ -2673,27 +2673,27 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
@@ -2715,27 +2715,27 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G520</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2338-0</t>
         </is>
       </c>
     </row>
@@ -2757,4351 +2757,4391 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G522</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2341-0</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2474-5</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2531-0</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2532-0</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2532-5</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-154M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4005</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7003</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4006</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7005</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4007</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7006</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8805</t>
+        </is>
+      </c>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8806</t>
+        </is>
+      </c>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="G153" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="G154" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="G155" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G156" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="G157" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU015</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2337-5</t>
         </is>
       </c>
     </row>
@@ -2777,4371 +2777,4386 @@
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2338-0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2340-5</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2341-0</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2532-0</t>
+          <t>JP2531-0</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2532-0</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-5</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-0</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-154M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2857</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PHC002</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3309</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>Q4001</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3310</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4003</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S7001</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4004</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7002</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8807</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8808</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8809</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="G160" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G161" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -452,22 +452,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G522</t>
         </is>
       </c>
     </row>
@@ -494,22 +494,22 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G524</t>
         </is>
       </c>
     </row>
@@ -536,22 +536,22 @@
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G525</t>
         </is>
       </c>
     </row>
@@ -578,22 +578,22 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G526</t>
         </is>
       </c>
     </row>
@@ -620,22 +620,22 @@
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G533</t>
         </is>
       </c>
     </row>
@@ -662,22 +662,22 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>G539</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -704,22 +704,22 @@
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G539</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -788,22 +788,22 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -830,22 +830,22 @@
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -872,22 +872,22 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -956,22 +956,22 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -998,22 +998,22 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -1040,22 +1040,22 @@
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -1124,22 +1124,22 @@
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -1208,22 +1208,22 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -1250,22 +1250,22 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -1292,22 +1292,22 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1334,22 +1334,22 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1376,22 +1376,22 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1502,22 +1502,22 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1544,22 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1581,27 +1581,27 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1623,27 +1623,27 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1665,27 +1665,27 @@
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1707,27 +1707,27 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>GWU015</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1749,27 +1749,27 @@
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU015</t>
         </is>
       </c>
     </row>
@@ -1791,27 +1791,27 @@
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1833,27 +1833,27 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1875,27 +1875,27 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1917,27 +1917,27 @@
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1959,27 +1959,27 @@
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -2001,27 +2001,27 @@
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -2043,27 +2043,27 @@
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACD6047</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -2085,27 +2085,27 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACD6047</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -2127,27 +2127,27 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -2169,27 +2169,27 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2752</t>
         </is>
       </c>
     </row>
@@ -2211,27 +2211,27 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -2253,27 +2253,27 @@
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -2295,27 +2295,27 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -2337,27 +2337,27 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -2379,27 +2379,27 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -2421,27 +2421,27 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -2463,27 +2463,27 @@
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2505,27 +2505,27 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2547,27 +2547,27 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
@@ -2589,27 +2589,27 @@
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2631,27 +2631,27 @@
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
@@ -2673,27 +2673,27 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
@@ -2715,27 +2715,27 @@
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G520</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
@@ -2757,4406 +2757,4426 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G520</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2335-6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2337-5</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PHC002</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2338-0</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4001</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4003</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2341-0</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4004</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2532-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-0</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2532-5</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-0</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>JP2546-0</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2543-0</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP2546-0</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-154M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>LE2857</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2857</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PHC001</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3307</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3309</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3310</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7001</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7002</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8807</t>
         </is>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8808</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="G164" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -2799,27 +2799,27 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PHC001</t>
         </is>
       </c>
     </row>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PHC002</t>
         </is>
       </c>
     </row>
@@ -2883,27 +2883,27 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>Q4001</t>
         </is>
       </c>
     </row>
@@ -2925,27 +2925,27 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>Q4003</t>
         </is>
       </c>
     </row>
@@ -2967,27 +2967,27 @@
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>Q4004</t>
         </is>
       </c>
     </row>
@@ -3009,27 +3009,27 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
@@ -3051,27 +3051,27 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
@@ -3093,27 +3093,27 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
@@ -3135,27 +3135,27 @@
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
@@ -3177,27 +3177,27 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
@@ -3219,27 +3219,27 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
@@ -3261,27 +3261,27 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
@@ -3303,27 +3303,27 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
@@ -3345,27 +3345,27 @@
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
@@ -3382,32 +3382,32 @@
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-580M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
@@ -3424,32 +3424,32 @@
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
@@ -3466,32 +3466,32 @@
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
@@ -3508,32 +3508,32 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
@@ -3550,32 +3550,32 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
@@ -3592,32 +3592,32 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
@@ -3634,32 +3634,32 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
@@ -3718,32 +3718,32 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
@@ -3760,32 +3760,32 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
@@ -3802,32 +3802,32 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
@@ -3844,32 +3844,32 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
@@ -3886,32 +3886,32 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3928,32 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
@@ -3970,32 +3970,32 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
@@ -4012,32 +4012,32 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
@@ -4054,32 +4054,32 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
@@ -4096,32 +4096,32 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4138,32 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
@@ -4180,32 +4180,32 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
@@ -4222,32 +4222,32 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
@@ -4264,32 +4264,32 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
@@ -4306,32 +4306,32 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
@@ -4348,32 +4348,32 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
@@ -4390,32 +4390,32 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4432,32 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
@@ -4516,32 +4516,32 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
@@ -4558,32 +4558,32 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
@@ -4600,32 +4600,32 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
@@ -4642,32 +4642,32 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
@@ -4684,32 +4684,32 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
@@ -4726,32 +4726,32 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
@@ -4768,32 +4768,32 @@
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
@@ -4852,32 +4852,32 @@
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
@@ -4894,32 +4894,32 @@
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
@@ -4936,32 +4936,32 @@
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
@@ -4978,32 +4978,32 @@
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
@@ -5020,32 +5020,32 @@
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
@@ -5062,32 +5062,32 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
@@ -5104,2079 +5104,2084 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>PB4</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3306</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3307</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3309</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3310</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S7001</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S7002</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8807</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8808</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8809</t>
         </is>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8810</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8811</t>
         </is>
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -2799,27 +2799,27 @@
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>PB4</t>
         </is>
       </c>
     </row>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PHC001</t>
         </is>
       </c>
     </row>
@@ -2883,27 +2883,27 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PHC002</t>
         </is>
       </c>
     </row>
@@ -2925,27 +2925,27 @@
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>Q4001</t>
         </is>
       </c>
     </row>
@@ -2967,27 +2967,27 @@
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>Q4003</t>
         </is>
       </c>
     </row>
@@ -3009,27 +3009,27 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>Q4004</t>
         </is>
       </c>
     </row>
@@ -3051,27 +3051,27 @@
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
@@ -3093,27 +3093,27 @@
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
@@ -3135,27 +3135,27 @@
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
@@ -3177,27 +3177,27 @@
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
@@ -3219,27 +3219,27 @@
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
@@ -3261,27 +3261,27 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
@@ -3303,27 +3303,27 @@
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
@@ -3345,27 +3345,27 @@
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
@@ -3387,27 +3387,27 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
@@ -3429,27 +3429,27 @@
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
@@ -3471,27 +3471,27 @@
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
@@ -3508,32 +3508,32 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-608M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
@@ -3550,32 +3550,32 @@
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
@@ -3592,32 +3592,32 @@
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
@@ -3634,32 +3634,32 @@
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
@@ -3676,32 +3676,32 @@
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
@@ -3718,32 +3718,32 @@
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
@@ -3760,32 +3760,32 @@
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
@@ -3802,32 +3802,32 @@
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
@@ -3844,32 +3844,32 @@
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
@@ -3886,32 +3886,32 @@
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3928,32 @@
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
@@ -3970,32 +3970,32 @@
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
@@ -4012,32 +4012,32 @@
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
@@ -4054,32 +4054,32 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
@@ -4096,32 +4096,32 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
@@ -4138,32 +4138,32 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
@@ -4180,32 +4180,32 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
@@ -4222,32 +4222,32 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
@@ -4264,32 +4264,32 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
@@ -4306,32 +4306,32 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
@@ -4348,32 +4348,32 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
@@ -4390,32 +4390,32 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
@@ -4432,32 +4432,32 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
@@ -4516,32 +4516,32 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
@@ -4558,32 +4558,32 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
@@ -4600,32 +4600,32 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
@@ -4642,32 +4642,32 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
@@ -4684,32 +4684,32 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
@@ -4726,32 +4726,32 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
@@ -4768,32 +4768,32 @@
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
@@ -4810,32 +4810,32 @@
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
@@ -4852,32 +4852,32 @@
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
@@ -4894,32 +4894,32 @@
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
@@ -4936,32 +4936,32 @@
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
@@ -4978,32 +4978,32 @@
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2515</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>S3301</t>
         </is>
       </c>
     </row>
@@ -5020,32 +5020,32 @@
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2516</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S3302</t>
         </is>
       </c>
     </row>
@@ -5062,32 +5062,32 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>PB1</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S3304</t>
         </is>
       </c>
     </row>
@@ -5104,2084 +5104,2089 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PB2</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3305</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3306</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3307</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3309</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3310</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S7001</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S7002</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8807</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8808</t>
         </is>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8809</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8810</t>
         </is>
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8811</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="G167" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -437,37 +437,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3VL80</t>
+          <t>3VL75</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G520</t>
         </is>
       </c>
     </row>
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>3VL81</t>
+          <t>3VL80</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G522</t>
         </is>
       </c>
     </row>
@@ -521,37 +521,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>3VL83</t>
+          <t>3VL81</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G524</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>3VL85</t>
+          <t>3VL83</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G525</t>
         </is>
       </c>
     </row>
@@ -605,37 +605,37 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3VL86</t>
+          <t>3VL85</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G526</t>
         </is>
       </c>
     </row>
@@ -647,37 +647,37 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>3VL87</t>
+          <t>3VL86</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G533</t>
         </is>
       </c>
     </row>
@@ -689,37 +689,37 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>3VL88</t>
+          <t>3VL87</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>G539</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -731,37 +731,37 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>3VL89</t>
+          <t>3VL88</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G539</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>3VL90</t>
+          <t>3VL89</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -815,37 +815,37 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3VL91</t>
+          <t>3VL90</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>3VL99</t>
+          <t>3VL91</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3VL100</t>
+          <t>3VL99</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>3VL101</t>
+          <t>3VL100</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -983,37 +983,37 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>3VL103</t>
+          <t>3VL101</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>3VL104</t>
+          <t>3VL103</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -1067,37 +1067,37 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>3VL105</t>
+          <t>3VL104</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>3VL106</t>
+          <t>3VL105</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1151,37 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>3VL107</t>
+          <t>3VL106</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>3VL109</t>
+          <t>3VL107</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -1235,37 +1235,37 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>3VL110</t>
+          <t>3VL109</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>3VL112</t>
+          <t>3VL110</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -1319,37 +1319,37 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3VL113</t>
+          <t>3VL112</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1361,37 +1361,37 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3VL114</t>
+          <t>3VL113</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1403,37 +1403,37 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3VL115</t>
+          <t>3VL114</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1445,37 +1445,37 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>3VL116</t>
+          <t>3VL115</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1487,22 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>3VL117</t>
+          <t>3VL116</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>3VL118</t>
+          <t>3VL117</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1571,37 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>3VL119</t>
+          <t>3VL118</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1613,37 +1613,37 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3VL120</t>
+          <t>3VL119</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3VL121</t>
+          <t>3VL120</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>3VL123</t>
+          <t>3VL121</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>3VL124</t>
+          <t>3VL123</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>GWU015</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1781,37 +1781,37 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>3VL125</t>
+          <t>3VL124</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU015</t>
         </is>
       </c>
     </row>
@@ -1823,37 +1823,37 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>3VL126</t>
+          <t>3VL125</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1865,37 +1865,37 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>3VL127</t>
+          <t>3VL126</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1907,37 +1907,37 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>3VL128</t>
+          <t>3VL127</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -1949,37 +1949,37 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>3VL131</t>
+          <t>3VL128</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -1991,37 +1991,37 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>3VL133</t>
+          <t>3VL131</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -2033,37 +2033,37 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>3VL134</t>
+          <t>3VL133</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -2075,37 +2075,37 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>3VL135</t>
+          <t>3VL134</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACD6047</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -2117,37 +2117,37 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>3VL136</t>
+          <t>3VL135</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACD6047</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -2159,37 +2159,37 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>3VL137</t>
+          <t>3VL136</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>HM2752</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -2201,37 +2201,37 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3VL139</t>
+          <t>3VL137</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2752</t>
         </is>
       </c>
     </row>
@@ -2243,37 +2243,37 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>3VR78</t>
+          <t>3VL139</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -2285,4908 +2285,4933 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>3VS93</t>
+          <t>3VR78</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>3VL59</t>
+          <t>3VL58</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>3VS94</t>
+          <t>3VS93</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>3VL62</t>
+          <t>3VL59</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>3VS95</t>
+          <t>3VS94</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>3VL63</t>
+          <t>3VL62</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>3VS96</t>
+          <t>3VS95</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>3VL64</t>
+          <t>3VL63</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>3VS97</t>
+          <t>3VS96</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>3VL65</t>
+          <t>3VL64</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>3VS98</t>
+          <t>3VS97</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>3VL68</t>
+          <t>3VL65</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3VS98</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>3VL70</t>
+          <t>3VL68</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>3VL71</t>
+          <t>3VL70</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>3VL72</t>
+          <t>3VL71</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>3VL74</t>
+          <t>3VL72</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G515</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>3VL75</t>
+          <t>3VL74</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G520</t>
+          <t>G519</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2333-6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2515</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2337-5</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2516</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2338-0</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PB1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2340-5</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PB2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2341-0</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PB4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PHC001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2532-0</t>
+          <t>JP2531-0</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PHC002</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2532-0</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4003</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4004</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP2537-0</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2537-0</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-580M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-580M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-608M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-608M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>JP2543-0</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2543-0</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>JP2546-0</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2546-0</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-154M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-870M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>LE2857</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-676M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2857</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-706M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2510</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL309</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2511</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL310</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2513</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S312</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2514</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S317</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3301</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3302</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3304</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8291</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8813</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3305</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3306</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3307</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3309</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3310</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7001</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7002</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8807</t>
         </is>
       </c>
       <c r="G167" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="G168" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="G169" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="G170" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -447,27 +447,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G520</t>
+          <t>G515</t>
         </is>
       </c>
     </row>
@@ -489,27 +489,27 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G519</t>
         </is>
       </c>
     </row>
@@ -531,27 +531,27 @@
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G520</t>
         </is>
       </c>
     </row>
@@ -573,27 +573,27 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G522</t>
         </is>
       </c>
     </row>
@@ -615,27 +615,27 @@
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G524</t>
         </is>
       </c>
     </row>
@@ -657,27 +657,27 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G525</t>
         </is>
       </c>
     </row>
@@ -699,27 +699,27 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G526</t>
         </is>
       </c>
     </row>
@@ -741,27 +741,27 @@
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>G539</t>
+          <t>G533</t>
         </is>
       </c>
     </row>
@@ -783,27 +783,27 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -825,27 +825,27 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G539</t>
         </is>
       </c>
     </row>
@@ -862,32 +862,32 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -904,32 +904,32 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -988,32 +988,32 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -1030,32 +1030,32 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -1072,32 +1072,32 @@
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -1156,32 +1156,32 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -1198,32 +1198,32 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -1240,32 +1240,32 @@
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -1282,32 +1282,32 @@
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -1324,32 +1324,32 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -1366,32 +1366,32 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -1408,32 +1408,32 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1450,32 +1450,32 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1492,32 +1492,32 @@
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1534,32 +1534,32 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1576,32 +1576,32 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1618,32 +1618,32 @@
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1660,32 +1660,32 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1702,32 +1702,32 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1744,32 +1744,32 @@
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
@@ -1786,32 +1786,32 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>GWU015</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
@@ -1828,32 +1828,32 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
@@ -1870,32 +1870,32 @@
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>GWU015</t>
         </is>
       </c>
     </row>
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
@@ -1954,32 +1954,32 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
@@ -1996,32 +1996,32 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
@@ -2038,32 +2038,32 @@
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
@@ -2080,32 +2080,32 @@
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
@@ -2122,32 +2122,32 @@
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACD6047</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
@@ -2164,32 +2164,32 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6047</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>HM2752</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
@@ -2248,32 +2248,32 @@
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
@@ -2290,32 +2290,32 @@
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2752</t>
         </is>
       </c>
     </row>
@@ -2332,32 +2332,32 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
@@ -2374,32 +2374,32 @@
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
@@ -2416,32 +2416,32 @@
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
@@ -2500,32 +2500,32 @@
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
@@ -2542,32 +2542,32 @@
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
@@ -2584,32 +2584,32 @@
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
@@ -2626,32 +2626,32 @@
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
@@ -2668,32 +2668,32 @@
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
@@ -2710,32 +2710,32 @@
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
@@ -2752,4466 +2752,4501 @@
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G514</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2510</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2333-6</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2511</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2335-6</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2513</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2337-5</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>P2514</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2338-0</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>P2515</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2340-5</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>P2516</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2341-0</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PB1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2532-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PB2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2531-0</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>PB4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-0</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>PHC001</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2532-5</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>PHC002</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4001</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4003</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JP2537-0</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4004</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-0</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-580M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-608M</t>
+          <t>MM-580M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>JP2543-0</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-608M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>JP2546-0</t>
+          <t>JP2543-0</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-0</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-870M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-154M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-870M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-676M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>LE2857</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-172M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-706M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2857</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-676M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-706M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-938M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2509</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>RL307</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>RL309</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="H115" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>RL310</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="H116" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S312</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8291</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8807</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S317</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8808</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3301</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8809</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3302</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8810</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3304</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8811</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3305</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8812</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3306</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8291</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8813</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S3307</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S3309</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S3310</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7001</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7002</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7004</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7013</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>WL02</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8610</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8772</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>X12-X14</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>SCT006</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8007</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8136</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8363</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8612</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8773</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>X31</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>SCT007</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8011</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8137</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8365</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8615</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8774</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>XP2000</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>SCT009</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8013</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8140</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8366</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8617</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8776</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>XP2003</t>
+          <t>VLINE-8891</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>SCT011</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8019</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8141</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8368</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8620</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8778</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>XP2004</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SCT013</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8020</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8142</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8369</t>
+          <t>VLINE-8339</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8625</t>
+          <t>VLINE-8605</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8779</t>
+          <t>VLINE-8770</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>XP2005</t>
+          <t>WH003</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SCT014</t>
+          <t>SCT002</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8023</t>
+          <t>VLINE-8004</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8144</t>
+          <t>VLINE-8134</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8403</t>
+          <t>VLINE-8362</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8630</t>
+          <t>VLINE-8610</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8780</t>
+          <t>VLINE-8772</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t>XP2007</t>
+          <t>WL02</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>SCT015</t>
+          <t>SCT006</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8025</t>
+          <t>VLINE-8007</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8145</t>
+          <t>VLINE-8136</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8404</t>
+          <t>VLINE-8363</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8671</t>
+          <t>VLINE-8612</t>
         </is>
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8781</t>
+          <t>VLINE-8773</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t>XP2008</t>
+          <t>X12-X14</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>SO2</t>
+          <t>SCT007</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8026</t>
+          <t>VLINE-8011</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8148</t>
+          <t>VLINE-8137</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8406</t>
+          <t>VLINE-8365</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8706</t>
+          <t>VLINE-8615</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8782</t>
+          <t>VLINE-8774</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>XP2010</t>
+          <t>X31</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>SSR101</t>
+          <t>SCT009</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8027</t>
+          <t>VLINE-8013</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8150</t>
+          <t>VLINE-8140</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8408</t>
+          <t>VLINE-8366</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8711</t>
+          <t>VLINE-8617</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8783</t>
+          <t>VLINE-8776</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>XP2011</t>
+          <t>XP2000</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>SSR102</t>
+          <t>SCT011</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8028</t>
+          <t>VLINE-8019</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8151</t>
+          <t>VLINE-8141</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8410</t>
+          <t>VLINE-8368</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8714</t>
+          <t>VLINE-8620</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8784</t>
+          <t>VLINE-8778</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>XP2012</t>
+          <t>XP2003</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>SSR103</t>
+          <t>SCT013</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8029</t>
+          <t>VLINE-8020</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8152</t>
+          <t>VLINE-8142</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8411</t>
+          <t>VLINE-8369</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8717</t>
+          <t>VLINE-8625</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8786</t>
+          <t>VLINE-8779</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t>XP2013</t>
+          <t>XP2004</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>SSR104</t>
+          <t>SCT014</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8030</t>
+          <t>VLINE-8023</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8153</t>
+          <t>VLINE-8144</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8413</t>
+          <t>VLINE-8403</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8720</t>
+          <t>VLINE-8630</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8787</t>
+          <t>VLINE-8780</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t>XP2014</t>
+          <t>XP2005</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>T363</t>
+          <t>SCT015</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8031</t>
+          <t>VLINE-8025</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8154</t>
+          <t>VLINE-8145</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8415</t>
+          <t>VLINE-8404</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8721</t>
+          <t>VLINE-8671</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8788</t>
+          <t>VLINE-8781</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>XP2015</t>
+          <t>XP2007</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>T386</t>
+          <t>SO2</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8032</t>
+          <t>VLINE-8026</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8155</t>
+          <t>VLINE-8148</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8417</t>
+          <t>VLINE-8406</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8723</t>
+          <t>VLINE-8706</t>
         </is>
       </c>
       <c r="F152" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8790</t>
+          <t>VLINE-8782</t>
         </is>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>XP2016</t>
+          <t>XP2008</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>TDX101</t>
+          <t>SSR101</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8036</t>
+          <t>VLINE-8027</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8157</t>
+          <t>VLINE-8150</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8418</t>
+          <t>VLINE-8408</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8725</t>
+          <t>VLINE-8711</t>
         </is>
       </c>
       <c r="F153" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8792</t>
+          <t>VLINE-8783</t>
         </is>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>XP2017</t>
+          <t>XP2010</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>TE2801</t>
+          <t>SSR102</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8038</t>
+          <t>VLINE-8028</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8158</t>
+          <t>VLINE-8151</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8419</t>
+          <t>VLINE-8410</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8726</t>
+          <t>VLINE-8714</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8793</t>
+          <t>VLINE-8784</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>XP2019</t>
+          <t>XP2011</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>TE2802</t>
+          <t>SSR103</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8042</t>
+          <t>VLINE-8029</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8159</t>
+          <t>VLINE-8152</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8420</t>
+          <t>VLINE-8411</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8727</t>
+          <t>VLINE-8717</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8794</t>
+          <t>VLINE-8786</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>XR552</t>
+          <t>XP2012</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>TE2803</t>
+          <t>SSR104</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8051</t>
+          <t>VLINE-8030</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8160</t>
+          <t>VLINE-8153</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8421</t>
+          <t>VLINE-8413</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8729</t>
+          <t>VLINE-8720</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8795</t>
+          <t>VLINE-8787</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>XRN001</t>
+          <t>XP2013</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>TE2804</t>
+          <t>T363</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8052</t>
+          <t>VLINE-8031</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8161</t>
+          <t>VLINE-8154</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8422</t>
+          <t>VLINE-8415</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8730</t>
+          <t>VLINE-8721</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8796</t>
+          <t>VLINE-8788</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>XRN004</t>
+          <t>XP2014</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>TE2805</t>
+          <t>T386</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8053</t>
+          <t>VLINE-8032</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8162</t>
+          <t>VLINE-8155</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8424</t>
+          <t>VLINE-8417</t>
         </is>
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8731</t>
+          <t>VLINE-8723</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8797</t>
+          <t>VLINE-8790</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>XRN005</t>
+          <t>XP2015</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>TE2806</t>
+          <t>TDX101</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8055</t>
+          <t>VLINE-8036</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8171</t>
+          <t>VLINE-8157</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8425</t>
+          <t>VLINE-8418</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8733</t>
+          <t>VLINE-8725</t>
         </is>
       </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8799</t>
+          <t>VLINE-8792</t>
         </is>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>XRN006</t>
+          <t>XP2016</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>TE2807</t>
+          <t>TE2801</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8056</t>
+          <t>VLINE-8038</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8172</t>
+          <t>VLINE-8158</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8426</t>
+          <t>VLINE-8419</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8735</t>
+          <t>VLINE-8726</t>
         </is>
       </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8800</t>
+          <t>VLINE-8793</t>
         </is>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>XRN007</t>
+          <t>XP2017</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>TE2808</t>
+          <t>TE2802</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8057</t>
+          <t>VLINE-8042</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8176</t>
+          <t>VLINE-8159</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8427</t>
+          <t>VLINE-8420</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8736</t>
+          <t>VLINE-8727</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8801</t>
+          <t>VLINE-8794</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>XRN009</t>
+          <t>XP2019</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>TE2809</t>
+          <t>TE2803</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8058</t>
+          <t>VLINE-8051</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8179</t>
+          <t>VLINE-8160</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8428</t>
+          <t>VLINE-8421</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8737</t>
+          <t>VLINE-8729</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8802</t>
+          <t>VLINE-8795</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>XRN011</t>
+          <t>XR552</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>TE2810</t>
+          <t>TE2804</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8059</t>
+          <t>VLINE-8052</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8180</t>
+          <t>VLINE-8161</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8429</t>
+          <t>VLINE-8422</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8739</t>
+          <t>VLINE-8730</t>
         </is>
       </c>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8803</t>
+          <t>VLINE-8796</t>
         </is>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>XRN014</t>
+          <t>XRN001</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>TE2812</t>
+          <t>TE2805</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8061</t>
+          <t>VLINE-8053</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8181</t>
+          <t>VLINE-8162</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8430</t>
+          <t>VLINE-8424</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8740</t>
+          <t>VLINE-8731</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8804</t>
+          <t>VLINE-8797</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN004</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2806</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8055</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8171</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8425</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8733</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8799</t>
         </is>
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN005</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2807</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8056</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8172</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8426</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8735</t>
         </is>
       </c>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8800</t>
         </is>
       </c>
       <c r="G166" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN006</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2808</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8057</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8176</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8427</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8736</t>
         </is>
       </c>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8801</t>
         </is>
       </c>
       <c r="G167" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN007</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TE2809</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8058</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8179</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8428</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8737</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8802</t>
         </is>
       </c>
       <c r="G168" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN009</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TE2810</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8059</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8180</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8429</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8739</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8803</t>
         </is>
       </c>
       <c r="G169" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN011</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>

--- a/downloads/loco_numbers_only.xlsx
+++ b/downloads/loco_numbers_only.xlsx
@@ -437,37 +437,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>3VL75</t>
+          <t>3VL74</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8114</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ACD6062</t>
+          <t>ACD6060</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>CF4425</t>
+          <t>CF4424</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>G515</t>
+          <t>G514</t>
         </is>
       </c>
     </row>
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>3VL80</t>
+          <t>3VL75</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>ACD6063</t>
+          <t>ACD6062</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>CF4426</t>
+          <t>CF4425</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>G519</t>
+          <t>G515</t>
         </is>
       </c>
     </row>
@@ -521,37 +521,37 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>3VL81</t>
+          <t>3VL80</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>9308</t>
         </is>
       </c>
       <c r="F3" s="1" t="inlineStr">
         <is>
-          <t>ACD6065</t>
+          <t>ACD6063</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>CF4427</t>
+          <t>CF4426</t>
         </is>
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>G520</t>
+          <t>G519</t>
         </is>
       </c>
     </row>
@@ -563,37 +563,37 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>3VL83</t>
+          <t>3VL81</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>9311</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>ACD6066</t>
+          <t>ACD6065</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>CF4428</t>
+          <t>CF4427</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>G522</t>
+          <t>G520</t>
         </is>
       </c>
     </row>
@@ -605,37 +605,37 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>3VL85</t>
+          <t>3VL83</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>ACD6067</t>
+          <t>ACD6066</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>CF4429</t>
+          <t>CF4428</t>
         </is>
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>G524</t>
+          <t>G522</t>
         </is>
       </c>
     </row>
@@ -647,37 +647,37 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>3VL86</t>
+          <t>3VL85</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3209</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>ACD6069</t>
+          <t>ACD6067</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>CF4431</t>
+          <t>CF4429</t>
         </is>
       </c>
       <c r="H6" s="1" t="inlineStr">
         <is>
-          <t>G525</t>
+          <t>G524</t>
         </is>
       </c>
     </row>
@@ -689,37 +689,37 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>3VL87</t>
+          <t>3VL86</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>ACD6071</t>
+          <t>ACD6069</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>CF4432</t>
+          <t>CF4431</t>
         </is>
       </c>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>G526</t>
+          <t>G525</t>
         </is>
       </c>
     </row>
@@ -731,37 +731,37 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>3VL88</t>
+          <t>3VL87</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>ACD6074</t>
+          <t>ACD6071</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>CF4434</t>
+          <t>CF4432</t>
         </is>
       </c>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>G533</t>
+          <t>G526</t>
         </is>
       </c>
     </row>
@@ -773,37 +773,37 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>3VL89</t>
+          <t>3VL88</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>ACD6075</t>
+          <t>ACD6074</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>CF4435</t>
+          <t>CF4434</t>
         </is>
       </c>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>G534</t>
+          <t>G533</t>
         </is>
       </c>
     </row>
@@ -815,37 +815,37 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3VL90</t>
+          <t>3VL89</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8138</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>ACN4141</t>
+          <t>ACD6075</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>CLF2</t>
+          <t>CF4435</t>
         </is>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>G539</t>
+          <t>G534</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>3VL91</t>
+          <t>3VL90</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>8142</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>ACN4142</t>
+          <t>ACN4141</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>CLF5</t>
+          <t>CLF2</t>
         </is>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
-          <t>G543</t>
+          <t>G539</t>
         </is>
       </c>
     </row>
@@ -899,37 +899,37 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>3VL99</t>
+          <t>3VL91</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>ACN4144</t>
+          <t>ACN4142</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>CLP8</t>
+          <t>CLF5</t>
         </is>
       </c>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>GL104</t>
+          <t>G543</t>
         </is>
       </c>
     </row>
@@ -941,37 +941,37 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>3VL100</t>
+          <t>3VL99</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>ACN4147</t>
+          <t>ACN4144</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>CLP13</t>
+          <t>CLP8</t>
         </is>
       </c>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>GL105</t>
+          <t>GL104</t>
         </is>
       </c>
     </row>
@@ -983,37 +983,37 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>3VL101</t>
+          <t>3VL100</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9407</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>ACN4148</t>
+          <t>ACN4147</t>
         </is>
       </c>
       <c r="G14" s="1" t="inlineStr">
         <is>
-          <t>CLP16</t>
+          <t>CLP13</t>
         </is>
       </c>
       <c r="H14" s="1" t="inlineStr">
         <is>
-          <t>GL108</t>
+          <t>GL105</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1025,37 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>3VL103</t>
+          <t>3VL101</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>ACN4149</t>
+          <t>ACN4148</t>
         </is>
       </c>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>CM3305</t>
+          <t>CLP16</t>
         </is>
       </c>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>GL109</t>
+          <t>GL108</t>
         </is>
       </c>
     </row>
@@ -1067,37 +1067,37 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>3VL104</t>
+          <t>3VL103</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>8163</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>ACN4150</t>
+          <t>ACN4149</t>
         </is>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>CM3307</t>
+          <t>CM3305</t>
         </is>
       </c>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>GL111</t>
+          <t>GL109</t>
         </is>
       </c>
     </row>
@@ -1109,37 +1109,37 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>3VL105</t>
+          <t>3VL104</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>8164</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>ACN4151</t>
+          <t>ACN4150</t>
         </is>
       </c>
       <c r="G17" s="1" t="inlineStr">
         <is>
-          <t>CM3309</t>
+          <t>CM3307</t>
         </is>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
-          <t>GM22</t>
+          <t>GL111</t>
         </is>
       </c>
     </row>
@@ -1151,37 +1151,37 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>3VL106</t>
+          <t>3VL105</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8164</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>ACN4152</t>
+          <t>ACN4151</t>
         </is>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>CM3310</t>
+          <t>CM3309</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>GM27</t>
+          <t>GM22</t>
         </is>
       </c>
     </row>
@@ -1193,37 +1193,37 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>3VL107</t>
+          <t>3VL106</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>44204</t>
+          <t>44202</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>ACN4168</t>
+          <t>ACN4152</t>
         </is>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>CSR006</t>
+          <t>CM3310</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>GM46</t>
+          <t>GM27</t>
         </is>
       </c>
     </row>
@@ -1235,37 +1235,37 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>3VL109</t>
+          <t>3VL107</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>8175</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44204</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>ACN4169</t>
+          <t>ACN4168</t>
         </is>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>CSR007</t>
+          <t>CSR006</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>GWA001</t>
+          <t>GM46</t>
         </is>
       </c>
     </row>
@@ -1277,37 +1277,37 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>3VL110</t>
+          <t>3VL109</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>44208</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>ACN4170</t>
+          <t>ACN4169</t>
         </is>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>CSR009</t>
+          <t>CSR007</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>GWA002</t>
+          <t>GWA001</t>
         </is>
       </c>
     </row>
@@ -1319,37 +1319,37 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>3VL112</t>
+          <t>3VL110</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>44209</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>ACN4171</t>
+          <t>ACN4170</t>
         </is>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>CSR010</t>
+          <t>CSR009</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>GWA004</t>
+          <t>GWA002</t>
         </is>
       </c>
     </row>
@@ -1361,37 +1361,37 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>3VL113</t>
+          <t>3VL112</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>8203</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>44217</t>
+          <t>44209</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
-          <t>ACN4172</t>
+          <t>ACN4171</t>
         </is>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>CSR011</t>
+          <t>CSR010</t>
         </is>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>GWA005</t>
+          <t>GWA004</t>
         </is>
       </c>
     </row>
@@ -1403,37 +1403,37 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>3VL114</t>
+          <t>3VL113</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>44220</t>
+          <t>44217</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
         <is>
-          <t>ACN4173</t>
+          <t>ACN4172</t>
         </is>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>CSR014</t>
+          <t>CSR011</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>GWA007</t>
+          <t>GWA005</t>
         </is>
       </c>
     </row>
@@ -1445,37 +1445,37 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>3VL115</t>
+          <t>3VL114</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>A4GTST</t>
+          <t>44220</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>ACN4174</t>
+          <t>ACN4173</t>
         </is>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>CSR015</t>
+          <t>CSR014</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>GWA010</t>
+          <t>GWA007</t>
         </is>
       </c>
     </row>
@@ -1487,37 +1487,37 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>3VL116</t>
+          <t>3VL115</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A4GTST</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>ACN4175</t>
+          <t>ACN4174</t>
         </is>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>CSR016</t>
+          <t>CSR015</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>GWB101</t>
+          <t>GWA010</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>3VL117</t>
+          <t>3VL116</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>8213</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>A70</t>
+          <t>A66</t>
         </is>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9050</t>
+          <t>ACN4175</t>
         </is>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>CSR017</t>
+          <t>CSR016</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>GWB102</t>
+          <t>GWB101</t>
         </is>
       </c>
     </row>
@@ -1571,37 +1571,37 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>3VL118</t>
+          <t>3VL117</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>AC4301</t>
+          <t>A70</t>
         </is>
       </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>AURIZON.9066</t>
+          <t>AURIZON.9050</t>
         </is>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>CSR018</t>
+          <t>CSR017</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>GWB103</t>
+          <t>GWB102</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1613,22 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>3VL119</t>
+          <t>3VL118</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>AC4302</t>
+          <t>AC4301</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>CSR019</t>
+          <t>CSR018</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>GWB105</t>
+          <t>GWB103</t>
         </is>
       </c>
     </row>
@@ -1655,37 +1655,37 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>3VL120</t>
+          <t>3VL119</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>8220</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>AC4303</t>
+          <t>AC4302</t>
         </is>
       </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>B75</t>
+          <t>AURIZON.9066</t>
         </is>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>CSR020</t>
+          <t>CSR019</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
-          <t>GWB106</t>
+          <t>GWB105</t>
         </is>
       </c>
     </row>
@@ -1697,37 +1697,37 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>3VL121</t>
+          <t>3VL120</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>AC4304</t>
+          <t>AC4303</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>BL29</t>
+          <t>B75</t>
         </is>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>CSR021</t>
+          <t>CSR020</t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
-          <t>GWU005</t>
+          <t>GWB106</t>
         </is>
       </c>
     </row>
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>3VL123</t>
+          <t>3VL121</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>AC4305</t>
+          <t>AC4304</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>BRM001</t>
+          <t>BL29</t>
         </is>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>CSR022</t>
+          <t>CSR021</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>GWU012</t>
+          <t>GWU005</t>
         </is>
       </c>
     </row>
@@ -1781,5472 +1781,5477 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>3VL124</t>
+          <t>3VL123</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>AC4308</t>
+          <t>AC4305</t>
         </is>
       </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>BX055</t>
+          <t>BRM001</t>
         </is>
       </c>
       <c r="G33" s="1" t="inlineStr">
         <is>
-          <t>CSR023</t>
+          <t>CSR022</t>
         </is>
       </c>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>GWU013</t>
+          <t>GWU012</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>3VL43</t>
+          <t>3VL42</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>3VL125</t>
+          <t>3VL124</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>ACB4401</t>
+          <t>AC4308</t>
         </is>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>C503</t>
+          <t>BX055</t>
         </is>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t>DS004</t>
+          <t>CSR023</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>GWU014</t>
+          <t>GWU013</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>3VL44</t>
+          <t>3VL43</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>3VL126</t>
+          <t>3VL125</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>ACB4402</t>
+          <t>ACB4401</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>C505</t>
+          <t>C503</t>
         </is>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>EA2501</t>
+          <t>DS004</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>GWU015</t>
+          <t>GWU014</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>3VL45</t>
+          <t>3VL44</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>3VL127</t>
+          <t>3VL126</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>ACB4403</t>
+          <t>ACB4402</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>C506</t>
+          <t>C505</t>
         </is>
       </c>
       <c r="G36" s="1" t="inlineStr">
         <is>
-          <t>EA2502</t>
+          <t>EA2501</t>
         </is>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>GWU015</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>3VL46</t>
+          <t>3VL45</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>3VL128</t>
+          <t>3VL127</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>8235</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>ACB4404</t>
+          <t>ACB4403</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>C507</t>
+          <t>C506</t>
         </is>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>EA2503</t>
+          <t>EA2502</t>
         </is>
       </c>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>HM2701</t>
+          <t>H3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>3VL47</t>
+          <t>3VL46</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>3VL131</t>
+          <t>3VL128</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>8236</t>
+          <t>8235</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>ACB4405</t>
+          <t>ACB4404</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>C508</t>
+          <t>C507</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>EA2504</t>
+          <t>EA2503</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>HM2702</t>
+          <t>HM2701</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>3VL48</t>
+          <t>3VL47</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>3VL133</t>
+          <t>3VL131</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>8236</t>
         </is>
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>ACB4406</t>
+          <t>ACB4405</t>
         </is>
       </c>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>C509</t>
+          <t>C508</t>
         </is>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>EA2505</t>
+          <t>EA2504</t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>HM2703</t>
+          <t>HM2702</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>3VL49</t>
+          <t>3VL48</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>3VL134</t>
+          <t>3VL133</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>ACC6030</t>
+          <t>ACB4406</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>C510</t>
+          <t>C509</t>
         </is>
       </c>
       <c r="G40" s="1" t="inlineStr">
         <is>
-          <t>EA2506</t>
+          <t>EA2505</t>
         </is>
       </c>
       <c r="H40" s="1" t="inlineStr">
         <is>
-          <t>HM2704</t>
+          <t>HM2703</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>3VL50</t>
+          <t>3VL49</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>3VL135</t>
+          <t>3VL134</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8240</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>ACC6031</t>
+          <t>ACC6030</t>
         </is>
       </c>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>CEY002</t>
+          <t>C510</t>
         </is>
       </c>
       <c r="G41" s="1" t="inlineStr">
         <is>
-          <t>EA2507</t>
+          <t>EA2506</t>
         </is>
       </c>
       <c r="H41" s="1" t="inlineStr">
         <is>
-          <t>HM2705</t>
+          <t>HM2704</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>3VL52</t>
+          <t>3VL50</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>3VL136</t>
+          <t>3VL135</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>ACC6032</t>
+          <t>ACC6031</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>CEY003</t>
+          <t>CEY002</t>
         </is>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>EA2508</t>
+          <t>EA2507</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>HM2706</t>
+          <t>HM2705</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>3VL53</t>
+          <t>3VL52</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>3VL137</t>
+          <t>3VL136</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>ACD6047</t>
+          <t>ACC6032</t>
         </is>
       </c>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>CEY004</t>
+          <t>CEY003</t>
         </is>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>EC2521</t>
+          <t>EA2508</t>
         </is>
       </c>
       <c r="H43" s="1" t="inlineStr">
         <is>
-          <t>HM2707</t>
+          <t>HM2706</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>3VL54</t>
+          <t>3VL53</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>3VL139</t>
+          <t>3VL137</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
         <is>
-          <t>8252</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>ACD6048</t>
+          <t>ACD6047</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>CEY005</t>
+          <t>CEY004</t>
         </is>
       </c>
       <c r="G44" s="1" t="inlineStr">
         <is>
-          <t>EC2522</t>
+          <t>EC2521</t>
         </is>
       </c>
       <c r="H44" s="1" t="inlineStr">
         <is>
-          <t>HM2751</t>
+          <t>HM2707</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>3VL55</t>
+          <t>3VL54</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>3VR78</t>
+          <t>3VL139</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>ACD6049</t>
+          <t>ACD6048</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>CEY007</t>
+          <t>CEY005</t>
         </is>
       </c>
       <c r="G45" s="1" t="inlineStr">
         <is>
-          <t>EC2523</t>
+          <t>EC2522</t>
         </is>
       </c>
       <c r="H45" s="1" t="inlineStr">
         <is>
-          <t>HM2752</t>
+          <t>HM2751</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>3VL58</t>
+          <t>3VL55</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>3VS93</t>
+          <t>3VR78</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6025</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>ACD6050</t>
+          <t>ACD6049</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>CF4401</t>
+          <t>CEY007</t>
         </is>
       </c>
       <c r="G46" s="1" t="inlineStr">
         <is>
-          <t>EC2524</t>
+          <t>EC2523</t>
         </is>
       </c>
       <c r="H46" s="1" t="inlineStr">
         <is>
-          <t>HM2753</t>
+          <t>HM2752</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>3VL59</t>
+          <t>3VL58</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>3VS94</t>
+          <t>3VS93</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>9027</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
         <is>
-          <t>ACD6051</t>
+          <t>ACD6050</t>
         </is>
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>CF4402</t>
+          <t>CF4401</t>
         </is>
       </c>
       <c r="G47" s="1" t="inlineStr">
         <is>
-          <t>EC2525</t>
+          <t>EC2524</t>
         </is>
       </c>
       <c r="H47" s="1" t="inlineStr">
         <is>
-          <t>HM2754</t>
+          <t>HM2753</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>3VL62</t>
+          <t>3VL59</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>3VS95</t>
+          <t>3VS94</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>ACD6052</t>
+          <t>ACD6051</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>CF4403</t>
+          <t>CF4402</t>
         </is>
       </c>
       <c r="G48" s="1" t="inlineStr">
         <is>
-          <t>EC2526</t>
+          <t>EC2525</t>
         </is>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
-          <t>HM2755</t>
+          <t>HM2754</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>3VL63</t>
+          <t>3VL62</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>3VS96</t>
+          <t>3VS95</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>9206</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>ACD6053</t>
+          <t>ACD6052</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>CF4404</t>
+          <t>CF4403</t>
         </is>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>EC2527</t>
+          <t>EC2526</t>
         </is>
       </c>
       <c r="H49" s="1" t="inlineStr">
         <is>
-          <t>HM2756</t>
+          <t>HM2755</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>3VL64</t>
+          <t>3VL63</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>3VS97</t>
+          <t>3VS96</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>8030</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>ACD6054</t>
+          <t>ACD6053</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>CF4405</t>
+          <t>CF4404</t>
         </is>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>EC2528</t>
+          <t>EC2527</t>
         </is>
       </c>
       <c r="H50" s="1" t="inlineStr">
         <is>
-          <t>HM2757</t>
+          <t>HM2756</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>3VL65</t>
+          <t>3VL64</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>3VS98</t>
+          <t>3VS97</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ACD6055</t>
+          <t>ACD6054</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>CF4409</t>
+          <t>CF4405</t>
         </is>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>FIE002</t>
+          <t>EC2528</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>JHRTST</t>
+          <t>HM2757</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>3VL68</t>
+          <t>3VL65</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3VS98</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ACD6056</t>
+          <t>ACD6055</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>CF4410</t>
+          <t>CF4409</t>
         </is>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>FIE003</t>
+          <t>FIE002</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>JP2296-5</t>
+          <t>JHRTST</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>3VL70</t>
+          <t>3VL68</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>ACD6057</t>
+          <t>ACD6056</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
         <is>
-          <t>CF4411</t>
+          <t>CF4410</t>
         </is>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>FIE004</t>
+          <t>FIE003</t>
         </is>
       </c>
       <c r="H53" s="1" t="inlineStr">
         <is>
-          <t>JP2296-6</t>
+          <t>JP2296-5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>3VL71</t>
+          <t>3VL70</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>ACD6058</t>
+          <t>ACD6057</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
         <is>
-          <t>CF4412</t>
+          <t>CF4411</t>
         </is>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>G512</t>
+          <t>FIE004</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>JP2297-0</t>
+          <t>JP2296-6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>3VL72</t>
+          <t>3VL71</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>ACD6059</t>
+          <t>ACD6058</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>CF4422</t>
+          <t>CF4412</t>
         </is>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>G513</t>
+          <t>G512</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>JP2298-5</t>
+          <t>JP2297-0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>3VL74</t>
+          <t>3VL72</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>ACD6060</t>
+          <t>ACD6059</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
         <is>
-          <t>CF4424</t>
+          <t>CF4422</t>
         </is>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>G514</t>
+          <t>G513</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>JP2299-6</t>
+          <t>JP2298-5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>JP2300-6</t>
+          <t>JP2299-6</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>MAN013</t>
+          <t>MAN012</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>MM-378M</t>
+          <t>MM-372M</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>MM-768M</t>
+          <t>MM-764M</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>MM-948M</t>
+          <t>MM-944M</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>MM-9961M</t>
+          <t>MM-9960M</t>
         </is>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>NR61</t>
+          <t>NR59</t>
         </is>
       </c>
       <c r="H58" s="1" t="inlineStr">
         <is>
-          <t>P2510</t>
+          <t>P2509</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>JP2333-6</t>
+          <t>JP2300-6</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>MAN014</t>
+          <t>MAN013</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>MM-382M</t>
+          <t>MM-378M</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
         <is>
-          <t>MM-774M</t>
+          <t>MM-768M</t>
         </is>
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>MM-952M</t>
+          <t>MM-948M</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
         <is>
-          <t>MM-9962M</t>
+          <t>MM-9961M</t>
         </is>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>NR62</t>
+          <t>NR61</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>P2511</t>
+          <t>P2510</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>JP2335-6</t>
+          <t>JP2333-6</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>MAN015</t>
+          <t>MAN014</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>MM-392M</t>
+          <t>MM-382M</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>MM-776M</t>
+          <t>MM-774M</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>MM-954M</t>
+          <t>MM-952M</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
         <is>
-          <t>MM-9963M</t>
+          <t>MM-9962M</t>
         </is>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>NR64</t>
+          <t>NR62</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>P2513</t>
+          <t>P2511</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>JP2337-5</t>
+          <t>JP2335-6</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>MAN016</t>
+          <t>MAN015</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>MM-418M</t>
+          <t>MM-392M</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>MM-778M</t>
+          <t>MM-776M</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>MM-956M</t>
+          <t>MM-954M</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>MM-9964M</t>
+          <t>MM-9963M</t>
         </is>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>NR65</t>
+          <t>NR64</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>P2514</t>
+          <t>P2513</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>JP2338-0</t>
+          <t>JP2337-5</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>MAN017</t>
+          <t>MAN016</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>MM-430M</t>
+          <t>MM-418M</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>MM-780M</t>
+          <t>MM-778M</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>MM-958M</t>
+          <t>MM-956M</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>MM-9965M</t>
+          <t>MM-9964M</t>
         </is>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>NR66</t>
+          <t>NR65</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>P2515</t>
+          <t>P2514</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>JP2340-5</t>
+          <t>JP2338-0</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>MM-4M</t>
+          <t>MAN017</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>MM-444M</t>
+          <t>MM-430M</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>MM-784M</t>
+          <t>MM-780M</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>MM-962M</t>
+          <t>MM-958M</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>MM-9966M</t>
+          <t>MM-9965M</t>
         </is>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t>NR67</t>
+          <t>NR66</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>P2516</t>
+          <t>P2515</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>JP2341-0</t>
+          <t>JP2340-5</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>MM-8M</t>
+          <t>MM-4M</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>MM-464M</t>
+          <t>MM-444M</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>MM-790M</t>
+          <t>MM-784M</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>MM-964M</t>
+          <t>MM-962M</t>
         </is>
       </c>
       <c r="F64" s="1" t="inlineStr">
         <is>
-          <t>MM-9967M</t>
+          <t>MM-9966M</t>
         </is>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>NR68</t>
+          <t>NR67</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>PB1</t>
+          <t>P2516</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>JP2474-5</t>
+          <t>JP2341-0</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>MM-9M</t>
+          <t>MM-8M</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>MM-486M</t>
+          <t>MM-464M</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>MM-792M</t>
+          <t>MM-790M</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>MM-966M</t>
+          <t>MM-964M</t>
         </is>
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>MM-9969M</t>
+          <t>MM-9967M</t>
         </is>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>NR69</t>
+          <t>NR68</t>
         </is>
       </c>
       <c r="H65" s="1" t="inlineStr">
         <is>
-          <t>PB2</t>
+          <t>PB1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>JP2531-0</t>
+          <t>JP2474-5</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>MM-16M</t>
+          <t>MM-9M</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>MM-496M</t>
+          <t>MM-486M</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>MM-796M</t>
+          <t>MM-792M</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>MM-968M</t>
+          <t>MM-966M</t>
         </is>
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>MM-9970M</t>
+          <t>MM-9969M</t>
         </is>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>NR71</t>
+          <t>NR69</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>PB4</t>
+          <t>PB2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>JP2532-0</t>
+          <t>JP2531-0</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>MM-18M</t>
+          <t>MM-16M</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>MM-514M</t>
+          <t>MM-496M</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>MM-798M</t>
+          <t>MM-796M</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>MM-970M</t>
+          <t>MM-968M</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>MMY032</t>
+          <t>MM-9970M</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>NR72</t>
+          <t>NR71</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>PHC001</t>
+          <t>PB4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>JP2532-5</t>
+          <t>JP2532-0</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>MM-20M</t>
+          <t>MM-18M</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>MM-526M</t>
+          <t>MM-514M</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>MM-800M</t>
+          <t>MM-798M</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>MM-972M</t>
+          <t>MM-970M</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
         <is>
-          <t>MRL001</t>
+          <t>MMY032</t>
         </is>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>NR75</t>
+          <t>NR72</t>
         </is>
       </c>
       <c r="H68" s="1" t="inlineStr">
         <is>
-          <t>PHC002</t>
+          <t>PHC001</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>JP2535-0</t>
+          <t>JP2532-5</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>MM-28M</t>
+          <t>MM-20M</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>MM-534M</t>
+          <t>MM-526M</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>MM-802M</t>
+          <t>MM-800M</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>MM-974M</t>
+          <t>MM-972M</t>
         </is>
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>MRL004</t>
+          <t>MRL001</t>
         </is>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>NR77</t>
+          <t>NR75</t>
         </is>
       </c>
       <c r="H69" s="1" t="inlineStr">
         <is>
-          <t>Q4001</t>
+          <t>PHC002</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>JP2535-5</t>
+          <t>JP2535-0</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>MM-34M</t>
+          <t>MM-28M</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>MM-536M</t>
+          <t>MM-534M</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>MM-804M</t>
+          <t>MM-802M</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>MM-976M</t>
+          <t>MM-974M</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>MRL006</t>
+          <t>MRL004</t>
         </is>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>NR78</t>
+          <t>NR77</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Q4003</t>
+          <t>Q4001</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>JP2536-0</t>
+          <t>JP2535-5</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>MM-42M</t>
+          <t>MM-34M</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>MM-542M</t>
+          <t>MM-536M</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
         <is>
-          <t>MM-808M</t>
+          <t>MM-804M</t>
         </is>
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>MM-980M</t>
+          <t>MM-976M</t>
         </is>
       </c>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>N452</t>
+          <t>MRL006</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>NR81</t>
+          <t>NR78</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
         <is>
-          <t>Q4004</t>
+          <t>Q4003</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>JP2536-5</t>
+          <t>JP2536-0</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>MM-46M</t>
+          <t>MM-42M</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>MM-544M</t>
+          <t>MM-542M</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>MM-810M</t>
+          <t>MM-808M</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>MM-982M</t>
+          <t>MM-980M</t>
         </is>
       </c>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>N453</t>
+          <t>N452</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>NR82</t>
+          <t>NR81</t>
         </is>
       </c>
       <c r="H72" s="1" t="inlineStr">
         <is>
-          <t>Q4005</t>
+          <t>Q4004</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>JP2537-0</t>
+          <t>JP2536-5</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>MM-50M</t>
+          <t>MM-46M</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>MM-546M</t>
+          <t>MM-544M</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>MM-814M</t>
+          <t>MM-810M</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>MM-984M</t>
+          <t>MM-982M</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>N457</t>
+          <t>N453</t>
         </is>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>NR83</t>
+          <t>NR82</t>
         </is>
       </c>
       <c r="H73" s="1" t="inlineStr">
         <is>
-          <t>Q4006</t>
+          <t>Q4005</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>JP2537-1</t>
+          <t>JP2537-0</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>MM-54M</t>
+          <t>MM-50M</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>MM-551M</t>
+          <t>MM-546M</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>MM-816M</t>
+          <t>MM-814M</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>MM-986M</t>
+          <t>MM-984M</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>N458</t>
+          <t>N457</t>
         </is>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>NR84</t>
+          <t>NR83</t>
         </is>
       </c>
       <c r="H74" s="1" t="inlineStr">
         <is>
-          <t>Q4007</t>
+          <t>Q4006</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>JP2537-5</t>
+          <t>JP2537-1</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>MM-58M</t>
+          <t>MM-54M</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>MM-552M</t>
+          <t>MM-551M</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>MM-818M</t>
+          <t>MM-816M</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>MM-9902M</t>
+          <t>MM-986M</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>N465</t>
+          <t>N458</t>
         </is>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t>NR85</t>
+          <t>NR84</t>
         </is>
       </c>
       <c r="H75" s="1" t="inlineStr">
         <is>
-          <t>Q4009</t>
+          <t>Q4007</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>JP2540-5</t>
+          <t>JP2537-5</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>MM-64M</t>
+          <t>MM-58M</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>MM-580M</t>
+          <t>MM-552M</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>MM-820M</t>
+          <t>MM-818M</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>MM-9903M</t>
+          <t>MM-9902M</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>N466</t>
+          <t>N465</t>
         </is>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t>NR86</t>
+          <t>NR85</t>
         </is>
       </c>
       <c r="H76" s="1" t="inlineStr">
         <is>
-          <t>Q4011</t>
+          <t>Q4009</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>JP2541-0</t>
+          <t>JP2540-5</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>MM-74M</t>
+          <t>MM-64M</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>MM-588M</t>
+          <t>MM-580M</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>MM-824M</t>
+          <t>MM-820M</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t>MM-9904M</t>
+          <t>MM-9903M</t>
         </is>
       </c>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>N467</t>
+          <t>N466</t>
         </is>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t>NR87</t>
+          <t>NR86</t>
         </is>
       </c>
       <c r="H77" s="1" t="inlineStr">
         <is>
-          <t>Q4012</t>
+          <t>Q4011</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>JP2542-1</t>
+          <t>JP2541-0</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>MM-76M</t>
+          <t>MM-74M</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>MM-602M</t>
+          <t>MM-588M</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>MM-826M</t>
+          <t>MM-824M</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t>MM-9906M</t>
+          <t>MM-9904M</t>
         </is>
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>N469</t>
+          <t>N467</t>
         </is>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>NR88</t>
+          <t>NR87</t>
         </is>
       </c>
       <c r="H78" s="1" t="inlineStr">
         <is>
-          <t>Q4013</t>
+          <t>Q4012</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>JP2542-5</t>
+          <t>JP2542-1</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>MM-82M</t>
+          <t>MM-76M</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>MM-608M</t>
+          <t>MM-602M</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>MM-828M</t>
+          <t>MM-826M</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>MM-9907M</t>
+          <t>MM-9906M</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>N473</t>
+          <t>N469</t>
         </is>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>NR89</t>
+          <t>NR88</t>
         </is>
       </c>
       <c r="H79" s="1" t="inlineStr">
         <is>
-          <t>Q4014</t>
+          <t>Q4013</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>JP2543-0</t>
+          <t>JP2542-5</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>MM-86M</t>
+          <t>MM-82M</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>MM-616M</t>
+          <t>MM-608M</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>MM-830M</t>
+          <t>MM-828M</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>MM-9908M</t>
+          <t>MM-9907M</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>NR1</t>
+          <t>N473</t>
         </is>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t>NR90</t>
+          <t>NR89</t>
         </is>
       </c>
       <c r="H80" s="1" t="inlineStr">
         <is>
-          <t>Q4015</t>
+          <t>Q4014</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>JP2544-6</t>
+          <t>JP2543-0</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>MM-88M</t>
+          <t>MM-86M</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>MM-624M</t>
+          <t>MM-616M</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>MM-832M</t>
+          <t>MM-830M</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>MM-9909M</t>
+          <t>MM-9908M</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>NR2</t>
+          <t>NR1</t>
         </is>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t>NR91</t>
+          <t>NR90</t>
         </is>
       </c>
       <c r="H81" s="1" t="inlineStr">
         <is>
-          <t>Q4016</t>
+          <t>Q4015</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>JP2546-0</t>
+          <t>JP2544-6</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>MM-90M</t>
+          <t>MM-88M</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MM-632M</t>
+          <t>MM-624M</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>MM-834M</t>
+          <t>MM-832M</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>MM-9912M</t>
+          <t>MM-9909M</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>NR4</t>
+          <t>NR2</t>
         </is>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t>NR92</t>
+          <t>NR91</t>
         </is>
       </c>
       <c r="H82" s="1" t="inlineStr">
         <is>
-          <t>Q4017</t>
+          <t>Q4016</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>JP2546-5</t>
+          <t>JP2546-0</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>MM-92M</t>
+          <t>MM-90M</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>MM-636M</t>
+          <t>MM-632M</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>MM-838M</t>
+          <t>MM-834M</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>MM-9913M</t>
+          <t>MM-9912M</t>
         </is>
       </c>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>NR5</t>
+          <t>NR4</t>
         </is>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t>NR93</t>
+          <t>NR92</t>
         </is>
       </c>
       <c r="H83" s="1" t="inlineStr">
         <is>
-          <t>Q4019</t>
+          <t>Q4017</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>JP9750-0</t>
+          <t>JP2546-5</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>MM-94M</t>
+          <t>MM-92M</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>MM-640M</t>
+          <t>MM-636M</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>MM-842M</t>
+          <t>MM-838M</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>MM-9914M</t>
+          <t>MM-9913M</t>
         </is>
       </c>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>NR7</t>
+          <t>NR5</t>
         </is>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t>NR94</t>
+          <t>NR93</t>
         </is>
       </c>
       <c r="H84" s="1" t="inlineStr">
         <is>
-          <t>QBX003</t>
+          <t>Q4019</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>JP9750-6</t>
+          <t>JP9750-0</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>MM-99M</t>
+          <t>MM-94M</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>MM-654M</t>
+          <t>MM-640M</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>MM-844M</t>
+          <t>MM-842M</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>MM-9915M</t>
+          <t>MM-9914M</t>
         </is>
       </c>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>NR8</t>
+          <t>NR7</t>
         </is>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t>NR95</t>
+          <t>NR94</t>
         </is>
       </c>
       <c r="H85" s="1" t="inlineStr">
         <is>
-          <t>QBX004</t>
+          <t>QBX003</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>LDP003</t>
+          <t>JP9750-6</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>MM-114M</t>
+          <t>MM-99M</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>MM-656M</t>
+          <t>MM-654M</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>MM-852M</t>
+          <t>MM-844M</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>MM-9917M</t>
+          <t>MM-9915M</t>
         </is>
       </c>
       <c r="F86" s="1" t="inlineStr">
         <is>
-          <t>NR9</t>
+          <t>NR8</t>
         </is>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>NR96</t>
+          <t>NR95</t>
         </is>
       </c>
       <c r="H86" s="1" t="inlineStr">
         <is>
-          <t>QBX005</t>
+          <t>QBX004</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>LDP007</t>
+          <t>LDP003</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>MM-120M</t>
+          <t>MM-114M</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>MM-660M</t>
+          <t>MM-656M</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>MM-858M</t>
+          <t>MM-852M</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>MM-9918M</t>
+          <t>MM-9917M</t>
         </is>
       </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>NR12</t>
+          <t>NR9</t>
         </is>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>NR98</t>
+          <t>NR96</t>
         </is>
       </c>
       <c r="H87" s="1" t="inlineStr">
         <is>
-          <t>QBX006</t>
+          <t>QBX005</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>LDP009</t>
+          <t>LDP007</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>MM-122M</t>
+          <t>MM-120M</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>MM-661M</t>
+          <t>MM-660M</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>MM-860M</t>
+          <t>MM-858M</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>MM-9919M</t>
+          <t>MM-9918M</t>
         </is>
       </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>NR15</t>
+          <t>NR12</t>
         </is>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>NR99</t>
+          <t>NR98</t>
         </is>
       </c>
       <c r="H88" s="1" t="inlineStr">
         <is>
-          <t>QE001</t>
+          <t>QBX006</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>LE2851</t>
+          <t>LDP009</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>MM-134M</t>
+          <t>MM-122M</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>MM-662M</t>
+          <t>MM-661M</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>MM-862M</t>
+          <t>MM-860M</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>MM-9920M</t>
+          <t>MM-9919M</t>
         </is>
       </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>NR16</t>
+          <t>NR15</t>
         </is>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>NR101</t>
+          <t>NR99</t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>QE002</t>
+          <t>QE001</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>LE2852</t>
+          <t>LE2851</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>MM-146M</t>
+          <t>MM-134M</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>MM-664M</t>
+          <t>MM-662M</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>MM-868M</t>
+          <t>MM-862M</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>MM-9922M</t>
+          <t>MM-9920M</t>
         </is>
       </c>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>NR18</t>
+          <t>NR16</t>
         </is>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>NR102</t>
+          <t>NR101</t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>QE003</t>
+          <t>QE002</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>LE2853</t>
+          <t>LE2852</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>MM-154M</t>
+          <t>MM-146M</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>MM-666M</t>
+          <t>MM-664M</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
         <is>
-          <t>MM-870M</t>
+          <t>MM-868M</t>
         </is>
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t>MM-9923M</t>
+          <t>MM-9922M</t>
         </is>
       </c>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>NR19</t>
+          <t>NR18</t>
         </is>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>NR103</t>
+          <t>NR102</t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>QE004</t>
+          <t>QE003</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>LE2854</t>
+          <t>LE2853</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>MM-168M</t>
+          <t>MM-154M</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>MM-668M</t>
+          <t>MM-666M</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
-          <t>MM-872M</t>
+          <t>MM-870M</t>
         </is>
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>MM-9924M</t>
+          <t>MM-9923M</t>
         </is>
       </c>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>NR21</t>
+          <t>NR19</t>
         </is>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t>NR105</t>
+          <t>NR103</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
-          <t>QE006</t>
+          <t>QE004</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>LE2855</t>
+          <t>LE2854</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>MM-172M</t>
+          <t>MM-168M</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>MM-673M</t>
+          <t>MM-668M</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
         <is>
-          <t>MM-874M</t>
+          <t>MM-872M</t>
         </is>
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>MM-9926M</t>
+          <t>MM-9924M</t>
         </is>
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>NR25</t>
+          <t>NR21</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>NR108</t>
+          <t>NR105</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
         <is>
-          <t>QL001</t>
+          <t>QE006</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>LE2856</t>
+          <t>LE2855</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>MM-182M</t>
+          <t>MM-172M</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>MM-674M</t>
+          <t>MM-673M</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>MM-876M</t>
+          <t>MM-874M</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>MM-9928M</t>
+          <t>MM-9926M</t>
         </is>
       </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
-          <t>NR27</t>
+          <t>NR25</t>
         </is>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>NR109</t>
+          <t>NR108</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>QL002</t>
+          <t>QL001</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>LE2857</t>
+          <t>LE2856</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>MM-184M</t>
+          <t>MM-182M</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t>MM-676M</t>
+          <t>MM-674M</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
         <is>
-          <t>MM-882M</t>
+          <t>MM-876M</t>
         </is>
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>MM-9929M</t>
+          <t>MM-9928M</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>NR28</t>
+          <t>NR27</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>NR110</t>
+          <t>NR109</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>QL004</t>
+          <t>QL002</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>LE2858</t>
+          <t>LE2857</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>MM-186M</t>
+          <t>MM-184M</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>MM-680M</t>
+          <t>MM-676M</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>MM-894M</t>
+          <t>MM-882M</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>MM-9932M</t>
+          <t>MM-9929M</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>NR30</t>
+          <t>NR28</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>NR111</t>
+          <t>NR110</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>QL007</t>
+          <t>QL004</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>LE2862</t>
+          <t>LE2858</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>MM-190M</t>
+          <t>MM-186M</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>MM-706M</t>
+          <t>MM-680M</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
         <is>
-          <t>MM-896M</t>
+          <t>MM-894M</t>
         </is>
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>MM-9933M</t>
+          <t>MM-9932M</t>
         </is>
       </c>
       <c r="F97" s="1" t="inlineStr">
         <is>
-          <t>NR31</t>
+          <t>NR30</t>
         </is>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>NR112</t>
+          <t>NR111</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>QL008</t>
+          <t>QL007</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>LE2863</t>
+          <t>LE2862</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>MM-196M</t>
+          <t>MM-190M</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>MM-708M</t>
+          <t>MM-706M</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>MM-902M</t>
+          <t>MM-896M</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>MM-9934M</t>
+          <t>MM-9933M</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>NR34</t>
+          <t>NR31</t>
         </is>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>NR113</t>
+          <t>NR112</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>QL010</t>
+          <t>QL008</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>LE2864</t>
+          <t>LE2863</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>MM-204M</t>
+          <t>MM-196M</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>MM-710M</t>
+          <t>MM-708M</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
-          <t>MM-904M</t>
+          <t>MM-902M</t>
         </is>
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>MM-9936M</t>
+          <t>MM-9934M</t>
         </is>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>NR36</t>
+          <t>NR34</t>
         </is>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>NR115</t>
+          <t>NR113</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>QL011</t>
+          <t>QL010</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>LZ3120</t>
+          <t>LE2864</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>MM-206M</t>
+          <t>MM-204M</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>MM-716M</t>
+          <t>MM-710M</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>MM-906M</t>
+          <t>MM-904M</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>MM-9938M</t>
+          <t>MM-9936M</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>NR37</t>
+          <t>NR36</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>NR118</t>
+          <t>NR115</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t>QL014</t>
+          <t>QL011</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>M24</t>
+          <t>LZ3120</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>MM-218M</t>
+          <t>MM-206M</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>MM-722M</t>
+          <t>MM-716M</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
-          <t>MM-908M</t>
+          <t>MM-906M</t>
         </is>
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>MM-9941M</t>
+          <t>MM-9938M</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>NR38</t>
+          <t>NR37</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>NR119</t>
+          <t>NR118</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
         <is>
-          <t>QL018</t>
+          <t>QL014</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>M24</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>MM-222M</t>
+          <t>MM-218M</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>MM-726M</t>
+          <t>MM-722M</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>MM-910M</t>
+          <t>MM-908M</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>MM-9943M</t>
+          <t>MM-9941M</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>NR39</t>
+          <t>NR38</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>NR120</t>
+          <t>NR119</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t>QR1744</t>
+          <t>QL018</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>MAN001</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>MM-224M</t>
+          <t>MM-222M</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>MM-728M</t>
+          <t>MM-726M</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
-          <t>MM-912M</t>
+          <t>MM-910M</t>
         </is>
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>MM-9945M</t>
+          <t>MM-9943M</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>NR40</t>
+          <t>NR39</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>NR122</t>
+          <t>NR120</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t>QR1771</t>
+          <t>QR1744</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>MAN002</t>
+          <t>MAN001</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>MM-242M</t>
+          <t>MM-224M</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t>MM-734M</t>
+          <t>MM-728M</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
-          <t>MM-914M</t>
+          <t>MM-912M</t>
         </is>
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>MM-9946M</t>
+          <t>MM-9945M</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>NR43</t>
+          <t>NR40</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>P14</t>
+          <t>NR122</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>QR5404</t>
+          <t>QR1771</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>MAN003</t>
+          <t>MAN002</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>MM-256M</t>
+          <t>MM-242M</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>MM-736M</t>
+          <t>MM-734M</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>MM-920M</t>
+          <t>MM-914M</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t>MM-9950M</t>
+          <t>MM-9946M</t>
         </is>
       </c>
       <c r="F105" s="1" t="inlineStr">
         <is>
-          <t>NR44</t>
+          <t>NR43</t>
         </is>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="H105" s="1" t="inlineStr">
         <is>
-          <t>R711</t>
+          <t>QR5404</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>MAN005</t>
+          <t>MAN003</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>MM-258M</t>
+          <t>MM-256M</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
         <is>
-          <t>MM-738M</t>
+          <t>MM-736M</t>
         </is>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
-          <t>MM-922M</t>
+          <t>MM-920M</t>
         </is>
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>MM-9951M</t>
+          <t>MM-9950M</t>
         </is>
       </c>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>NR45</t>
+          <t>NR44</t>
         </is>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>P2501</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>R766</t>
+          <t>R711</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>MAN006</t>
+          <t>MAN005</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>MM-264M</t>
+          <t>MM-258M</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>MM-740M</t>
+          <t>MM-738M</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>MM-924M</t>
+          <t>MM-922M</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>MM-9952M</t>
+          <t>MM-9951M</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>NR48</t>
+          <t>NR45</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>P2502</t>
+          <t>P2501</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>RB2353</t>
+          <t>R766</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>MAN007</t>
+          <t>MAN006</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>MM-268M</t>
+          <t>MM-264M</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>MM-742M</t>
+          <t>MM-740M</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>MM-926M</t>
+          <t>MM-924M</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>MM-9953M</t>
+          <t>MM-9952M</t>
         </is>
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>NR51</t>
+          <t>NR48</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t>P2503</t>
+          <t>P2502</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
         <is>
-          <t>RCTST4</t>
+          <t>RB2353</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>MAN008</t>
+          <t>MAN007</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>MM-278M</t>
+          <t>MM-268M</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>MM-744M</t>
+          <t>MM-742M</t>
         </is>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
-          <t>MM-934M</t>
+          <t>MM-926M</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>MM-9954M</t>
+          <t>MM-9953M</t>
         </is>
       </c>
       <c r="F109" s="1" t="inlineStr">
         <is>
-          <t>NR52</t>
+          <t>NR51</t>
         </is>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>P2505</t>
+          <t>P2503</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>RL301</t>
+          <t>RCTST4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>MAN009</t>
+          <t>MAN008</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>MM-282M</t>
+          <t>MM-278M</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>MM-752M</t>
+          <t>MM-744M</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>MM-936M</t>
+          <t>MM-934M</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>MM-9955M</t>
+          <t>MM-9954M</t>
         </is>
       </c>
       <c r="F110" s="1" t="inlineStr">
         <is>
-          <t>NR53</t>
+          <t>NR52</t>
         </is>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>P2506</t>
+          <t>P2505</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>RL302</t>
+          <t>RL301</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>MAN010</t>
+          <t>MAN009</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>MM-352M</t>
+          <t>MM-282M</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>MM-756M</t>
+          <t>MM-752M</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
-          <t>MM-938M</t>
+          <t>MM-936M</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>MM-9957M</t>
+          <t>MM-9955M</t>
         </is>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>NR54</t>
+          <t>NR53</t>
         </is>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t>P2507</t>
+          <t>P2506</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>RL304</t>
+          <t>RL302</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>MAN011</t>
+          <t>MAN010</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>MM-358M</t>
+          <t>MM-352M</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>MM-760M</t>
+          <t>MM-756M</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>MM-940M</t>
+          <t>MM-938M</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>MM-9959M</t>
+          <t>MM-9957M</t>
         </is>
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>NR57</t>
+          <t>NR54</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>P2508</t>
+          <t>P2507</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>RL305</t>
+          <t>RL304</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>MAN012</t>
+          <t>MAN011</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>MM-372M</t>
+          <t>MM-358M</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>MM-764M</t>
+          <t>MM-760M</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t>MM-944M</t>
+          <t>MM-940M</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>MM-9960M</t>
+          <t>MM-9959M</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>NR59</t>
+          <t>NR57</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t>P2509</t>
+          <t>P2508</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>RL307</t>
+          <t>RL305</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>RL309</t>
+          <t>RL307</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>TE2813</t>
+          <t>TE2812</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8072</t>
+          <t>VLINE-8061</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8182</t>
+          <t>VLINE-8181</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8431</t>
+          <t>VLINE-8430</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8741</t>
+          <t>VLINE-8740</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8805</t>
+          <t>VLINE-8804</t>
         </is>
       </c>
       <c r="H115" s="1" t="inlineStr">
         <is>
-          <t>XRN017</t>
+          <t>XRN014</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>RL310</t>
+          <t>RL309</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>TE2814</t>
+          <t>TE2813</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8074</t>
+          <t>VLINE-8072</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8183</t>
+          <t>VLINE-8182</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8432</t>
+          <t>VLINE-8431</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8742</t>
+          <t>VLINE-8741</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8806</t>
+          <t>VLINE-8805</t>
         </is>
       </c>
       <c r="H116" s="1" t="inlineStr">
         <is>
-          <t>XRN018</t>
+          <t>XRN017</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>S312</t>
+          <t>RL310</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>TJ096</t>
+          <t>TE2814</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8075</t>
+          <t>VLINE-8074</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8184</t>
+          <t>VLINE-8183</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8433</t>
+          <t>VLINE-8432</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8743</t>
+          <t>VLINE-8742</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8807</t>
+          <t>VLINE-8806</t>
         </is>
       </c>
       <c r="H117" s="1" t="inlineStr">
         <is>
-          <t>XRN020</t>
+          <t>XRN018</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>S317</t>
+          <t>S312</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>TJ107</t>
+          <t>TJ096</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8076</t>
+          <t>VLINE-8075</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8185</t>
+          <t>VLINE-8184</t>
         </is>
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8434</t>
+          <t>VLINE-8433</t>
         </is>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8744</t>
+          <t>VLINE-8743</t>
         </is>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8808</t>
+          <t>VLINE-8807</t>
         </is>
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
-          <t>XRN021</t>
+          <t>XRN020</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>S3301</t>
+          <t>S317</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>TT03</t>
+          <t>TJ107</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8077</t>
+          <t>VLINE-8076</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8186</t>
+          <t>VLINE-8185</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8435</t>
+          <t>VLINE-8434</t>
         </is>
       </c>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8745</t>
+          <t>VLINE-8744</t>
         </is>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8809</t>
+          <t>VLINE-8808</t>
         </is>
       </c>
       <c r="H119" s="1" t="inlineStr">
         <is>
-          <t>XRN023</t>
+          <t>XRN021</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>S3302</t>
+          <t>S3301</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>TT04</t>
+          <t>TT03</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8080</t>
+          <t>VLINE-8077</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8187</t>
+          <t>VLINE-8186</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8438</t>
+          <t>VLINE-8435</t>
         </is>
       </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8746</t>
+          <t>VLINE-8745</t>
         </is>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8810</t>
+          <t>VLINE-8809</t>
         </is>
       </c>
       <c r="H120" s="1" t="inlineStr">
         <is>
-          <t>XRN025</t>
+          <t>XRN023</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>S3304</t>
+          <t>S3302</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>TT05</t>
+          <t>TT04</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8081</t>
+          <t>VLINE-8080</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8188</t>
+          <t>VLINE-8187</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8440</t>
+          <t>VLINE-8438</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8747</t>
+          <t>VLINE-8746</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8811</t>
+          <t>VLINE-8810</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr">
         <is>
-          <t>XRN026</t>
+          <t>XRN025</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>S3305</t>
+          <t>S3304</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>TT07</t>
+          <t>TT05</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8084</t>
+          <t>VLINE-8081</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8189</t>
+          <t>VLINE-8188</t>
         </is>
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8441</t>
+          <t>VLINE-8440</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8748</t>
+          <t>VLINE-8747</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8812</t>
+          <t>VLINE-8811</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr">
         <is>
-          <t>XRN027</t>
+          <t>XRN026</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>S3306</t>
+          <t>S3305</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>TT08</t>
+          <t>TT07</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8088</t>
+          <t>VLINE-8084</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8291</t>
+          <t>VLINE-8189</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8442</t>
+          <t>VLINE-8441</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8749</t>
+          <t>VLINE-8748</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8813</t>
+          <t>VLINE-8812</t>
         </is>
       </c>
       <c r="H123" s="1" t="inlineStr">
         <is>
-          <t>Y163</t>
+          <t>XRN027</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>S3307</t>
+          <t>S3306</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>TT103</t>
+          <t>TT08</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8089</t>
+          <t>VLINE-8088</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8293</t>
+          <t>VLINE-8291</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8443</t>
+          <t>VLINE-8442</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8750</t>
+          <t>VLINE-8749</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8814</t>
+          <t>VLINE-8813</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>Y163</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>S3309</t>
+          <t>S3307</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>TT106</t>
+          <t>TT103</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8104</t>
+          <t>VLINE-8089</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8303</t>
+          <t>VLINE-8293</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8444</t>
+          <t>VLINE-8443</t>
         </is>
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8751</t>
+          <t>VLINE-8750</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8816</t>
+          <t>VLINE-8814</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>S3310</t>
+          <t>S3309</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>TT107</t>
+          <t>TT106</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8107</t>
+          <t>VLINE-8104</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8304</t>
+          <t>VLINE-8303</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8446</t>
+          <t>VLINE-8444</t>
         </is>
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8752</t>
+          <t>VLINE-8751</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8817</t>
+          <t>VLINE-8816</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>S7001</t>
+          <t>S3310</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>TT108</t>
+          <t>TT107</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8110</t>
+          <t>VLINE-8107</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8306</t>
+          <t>VLINE-8304</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8447</t>
+          <t>VLINE-8446</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8753</t>
+          <t>VLINE-8752</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8818</t>
+          <t>VLINE-8817</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>S7002</t>
+          <t>S7001</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>TT110</t>
+          <t>TT108</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8111</t>
+          <t>VLINE-8110</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8311</t>
+          <t>VLINE-8306</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8449</t>
+          <t>VLINE-8447</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8754</t>
+          <t>VLINE-8753</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8819</t>
+          <t>VLINE-8818</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>S7003</t>
+          <t>S7002</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>TT113</t>
+          <t>TT110</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8113</t>
+          <t>VLINE-8111</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8313</t>
+          <t>VLINE-8311</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8450</t>
+          <t>VLINE-8449</t>
         </is>
       </c>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8755</t>
+          <t>VLINE-8754</t>
         </is>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8822</t>
+          <t>VLINE-8819</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>S7004</t>
+          <t>S7003</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>TT114</t>
+          <t>TT113</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8114</t>
+          <t>VLINE-8113</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8314</t>
+          <t>VLINE-8313</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8451</t>
+          <t>VLINE-8450</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8756</t>
+          <t>VLINE-8755</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8860</t>
+          <t>VLINE-8822</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>S7005</t>
+          <t>S7004</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>TT115</t>
+          <t>TT114</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8115</t>
+          <t>VLINE-8114</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8316</t>
+          <t>VLINE-8314</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8452</t>
+          <t>VLINE-8451</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8757</t>
+          <t>VLINE-8756</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8861</t>
+          <t>VLINE-8860</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>S7006</t>
+          <t>S7005</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>TT116</t>
+          <t>TT115</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8119</t>
+          <t>VLINE-8115</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8318</t>
+          <t>VLINE-8316</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8453</t>
+          <t>VLINE-8452</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8758</t>
+          <t>VLINE-8757</t>
         </is>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8862</t>
+          <t>VLINE-8861</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>S7007</t>
+          <t>S7006</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>TT117</t>
+          <t>TT116</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8120</t>
+          <t>VLINE-8119</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8321</t>
+          <t>VLINE-8318</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8454</t>
+          <t>VLINE-8453</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8759</t>
+          <t>VLINE-8758</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8863</t>
+          <t>VLINE-8862</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>S7008</t>
+          <t>S7007</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>TT122</t>
+          <t>TT117</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8121</t>
+          <t>VLINE-8120</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8323</t>
+          <t>VLINE-8321</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8455</t>
+          <t>VLINE-8454</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8760</t>
+          <t>VLINE-8759</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8864</t>
+          <t>VLINE-8863</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>S7012</t>
+          <t>S7008</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>TT127</t>
+          <t>TT122</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8123</t>
+          <t>VLINE-8121</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8324</t>
+          <t>VLINE-8323</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8456</t>
+          <t>VLINE-8455</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8761</t>
+          <t>VLINE-8760</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8865</t>
+          <t>VLINE-8864</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>S7013</t>
+          <t>S7012</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>TT128</t>
+          <t>TT127</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8124</t>
+          <t>VLINE-8123</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8325</t>
+          <t>VLINE-8324</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8457</t>
+          <t>VLINE-8456</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8762</t>
+          <t>VLINE-8761</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8866</t>
+          <t>VLINE-8865</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>S7014</t>
+          <t>S7013</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>TT130</t>
+          <t>TT128</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8126</t>
+          <t>VLINE-8124</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8328</t>
+          <t>VLINE-8325</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8460</t>
+          <t>VLINE-8457</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8763</t>
+          <t>VLINE-8762</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8867</t>
+          <t>VLINE-8866</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>S7015</t>
+          <t>S7014</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>TT131</t>
+          <t>TT130</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8127</t>
+          <t>VLINE-8126</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8329</t>
+          <t>VLINE-8328</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8461</t>
+          <t>VLINE-8460</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8765</t>
+          <t>VLINE-8763</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8868</t>
+          <t>VLINE-8867</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>S7017</t>
+          <t>S7015</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>TT202</t>
+          <t>TT131</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8128</t>
+          <t>VLINE-8127</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8332</t>
+          <t>VLINE-8329</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8464</t>
+          <t>VLINE-8461</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8766</t>
+          <t>VLINE-8765</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8869</t>
+          <t>VLINE-8868</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>S7018</t>
+          <t>S7017</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>TT206</t>
+          <t>TT202</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8129</t>
+          <t>VLINE-8128</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8336</t>
+          <t>VLINE-8332</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8465</t>
+          <t>VLINE-8464</t>
         </is>
       </c>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8767</t>
+          <t>VLINE-8766</t>
         </is>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8890</t>
+          <t>VLINE-8869</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>S7020</t>
+          <t>S7018</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>VL352</t>
+          <t>TT206</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8131</t>
+          <t>VLINE-8129</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8337</t>
+          <t>VLINE-8336</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8468</t>
+          <t>VLINE-8465</t>
         </is>
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8768</t>
+          <t>VLINE-8767</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8891</t>
+          <t>VLINE-8890</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>S7022</t>
+          <t>S7020</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>VL353</t>
+          <t>VL352</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8132</t>
+          <t>VLINE-8131</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8338</t>
+          <t>VLINE-8337</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8469</t>
+          <t>VLINE-8468</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8769</t>
+          <t>VLINE-8768</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>WH001</t>
+          <t>VLINE-8891</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>SCT001</t>
+          <t>S7022</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>VL357</t>
+          <t>VL353</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8133</t>
+          <t>VLINE-8132</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8339</t>
+          <t>VLINE-8338</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8605</t>
+          <t>VLINE-8469</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8770</t>
+          <t>VLINE-8769</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>WH003</t>
+          <t>WH001</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>SCT002</t>
+          <t>SCT001</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8004</t>
+          <t>VL357</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8134</t>
+          <t>VLINE-8133</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>VLINE-8362</t>
+          <t>VLINE-8339</t>
         </is>